--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e36746ea3f026f8f/Documenti/GitHub/Dilah96.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB12CD19-8189-4DD7-8507-5C7FF8CCC1EF}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4E4B81-441F-41A7-8872-253D72B81C3E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alimenti" sheetId="1" r:id="rId1"/>
@@ -1248,7 +1248,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1268,22 +1268,8 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="24">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1386,44 +1372,8 @@
         <bgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1446,52 +1396,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1571,50 +1480,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="23" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="22" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="23" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1883,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M357"/>
+  <dimension ref="A1:M358"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1894,8 +1759,9 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11356,2897 +11222,2995 @@
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A271" s="49" t="s">
+      <c r="A271" s="44" t="s">
         <v>297</v>
       </c>
-      <c r="B271" s="50">
+      <c r="B271" s="45">
         <v>530</v>
       </c>
-      <c r="C271" s="51">
+      <c r="C271" s="45">
         <v>29</v>
       </c>
-      <c r="D271" s="51">
+      <c r="D271" s="45">
         <v>8.6</v>
       </c>
-      <c r="E271" s="52">
+      <c r="E271" s="45">
         <v>60</v>
       </c>
-      <c r="F271" s="52">
+      <c r="F271" s="45">
         <v>20</v>
       </c>
-      <c r="G271" s="53">
+      <c r="G271" s="45">
         <v>6.2</v>
       </c>
-      <c r="H271" s="54">
+      <c r="H271" s="45">
         <v>8</v>
       </c>
-      <c r="I271" s="55">
+      <c r="I271" s="45">
         <v>1.7</v>
       </c>
-      <c r="J271" s="56"/>
-      <c r="K271" s="57">
+      <c r="J271" s="45"/>
+      <c r="K271" s="46">
         <v>45180</v>
       </c>
-      <c r="L271" s="49" t="s">
+      <c r="L271" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="M271" s="47"/>
+      <c r="M271" s="44"/>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A272" s="49" t="s">
+      <c r="A272" s="44" t="s">
         <v>299</v>
       </c>
-      <c r="B272" s="50">
+      <c r="B272" s="45">
         <v>194</v>
       </c>
-      <c r="C272" s="51">
+      <c r="C272" s="45">
         <v>12.7</v>
       </c>
-      <c r="D272" s="51">
-        <v>0</v>
-      </c>
-      <c r="E272" s="52">
-        <v>0</v>
-      </c>
-      <c r="F272" s="52">
-        <v>0</v>
-      </c>
-      <c r="G272" s="53">
-        <v>0</v>
-      </c>
-      <c r="H272" s="54">
+      <c r="D272" s="45">
+        <v>0</v>
+      </c>
+      <c r="E272" s="45">
+        <v>0</v>
+      </c>
+      <c r="F272" s="45">
+        <v>0</v>
+      </c>
+      <c r="G272" s="45">
+        <v>0</v>
+      </c>
+      <c r="H272" s="45">
         <v>19.899999999999999</v>
       </c>
-      <c r="I272" s="55">
+      <c r="I272" s="45">
         <v>1.2</v>
       </c>
-      <c r="J272" s="56"/>
-      <c r="K272" s="57">
+      <c r="J272" s="45"/>
+      <c r="K272" s="46">
         <v>45183</v>
       </c>
-      <c r="L272" s="49"/>
+      <c r="L272" s="44"/>
+      <c r="M272" s="44"/>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A273" s="58" t="s">
+      <c r="A273" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="B273" s="59">
+      <c r="B273" s="45">
         <v>329</v>
       </c>
-      <c r="C273" s="60">
+      <c r="C273" s="45">
         <v>32</v>
       </c>
-      <c r="D273" s="60">
+      <c r="D273" s="45">
         <v>23</v>
       </c>
-      <c r="E273" s="61">
+      <c r="E273" s="45">
         <v>13</v>
       </c>
-      <c r="F273" s="61">
-        <v>0</v>
-      </c>
-      <c r="G273" s="62">
-        <v>0</v>
-      </c>
-      <c r="H273" s="63">
+      <c r="F273" s="45">
+        <v>0</v>
+      </c>
+      <c r="G273" s="45">
+        <v>0</v>
+      </c>
+      <c r="H273" s="45">
         <v>22</v>
       </c>
-      <c r="I273" s="64">
+      <c r="I273" s="45">
         <v>1.8</v>
       </c>
-      <c r="J273" s="65"/>
-      <c r="K273" s="49"/>
-      <c r="L273" s="49"/>
-      <c r="M273" s="48"/>
+      <c r="J273" s="45"/>
+      <c r="K273" s="46"/>
+      <c r="L273" s="44"/>
+      <c r="M273" s="44"/>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A274" s="58" t="s">
+      <c r="A274" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="B274" s="59">
+      <c r="B274" s="45">
         <v>238</v>
       </c>
-      <c r="C274" s="60">
+      <c r="C274" s="45">
         <v>23</v>
       </c>
-      <c r="D274" s="60">
-        <v>0</v>
-      </c>
-      <c r="E274" s="61">
+      <c r="D274" s="45">
+        <v>0</v>
+      </c>
+      <c r="E274" s="45">
         <v>1.8</v>
       </c>
-      <c r="F274" s="61">
+      <c r="F274" s="45">
         <v>1.8</v>
       </c>
-      <c r="G274" s="62">
+      <c r="G274" s="45">
         <v>3.3</v>
       </c>
-      <c r="H274" s="63">
+      <c r="H274" s="45">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I274" s="64">
-        <v>0</v>
-      </c>
-      <c r="J274" s="65"/>
-      <c r="K274" s="57">
+      <c r="I274" s="45">
+        <v>0</v>
+      </c>
+      <c r="J274" s="45"/>
+      <c r="K274" s="46">
         <v>45187</v>
       </c>
-      <c r="L274" s="49"/>
-      <c r="M274" s="48"/>
+      <c r="L274" s="44"/>
+      <c r="M274" s="44"/>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A275" s="58" t="s">
+      <c r="A275" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="B275" s="59"/>
-      <c r="C275" s="60"/>
-      <c r="D275" s="60"/>
-      <c r="E275" s="61"/>
-      <c r="F275" s="61"/>
-      <c r="G275" s="62"/>
-      <c r="H275" s="63"/>
-      <c r="I275" s="64"/>
-      <c r="J275" s="65"/>
-      <c r="K275" s="49"/>
-      <c r="L275" s="49"/>
-      <c r="M275" s="48"/>
+      <c r="B275" s="45"/>
+      <c r="C275" s="45"/>
+      <c r="D275" s="45"/>
+      <c r="E275" s="45"/>
+      <c r="F275" s="45"/>
+      <c r="G275" s="45"/>
+      <c r="H275" s="45"/>
+      <c r="I275" s="45"/>
+      <c r="J275" s="45"/>
+      <c r="K275" s="46"/>
+      <c r="L275" s="44"/>
+      <c r="M275" s="44"/>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A276" s="58" t="s">
+      <c r="A276" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="B276" s="59">
+      <c r="B276" s="45">
         <v>393</v>
       </c>
-      <c r="C276" s="60">
+      <c r="C276" s="45">
         <v>37.1</v>
       </c>
-      <c r="D276" s="60">
+      <c r="D276" s="45">
         <v>12.6</v>
       </c>
-      <c r="E276" s="61">
-        <v>0</v>
-      </c>
-      <c r="F276" s="61">
-        <v>0</v>
-      </c>
-      <c r="G276" s="62">
-        <v>0</v>
-      </c>
-      <c r="H276" s="63">
+      <c r="E276" s="45">
+        <v>0</v>
+      </c>
+      <c r="F276" s="45">
+        <v>0</v>
+      </c>
+      <c r="G276" s="45">
+        <v>0</v>
+      </c>
+      <c r="H276" s="45">
         <v>13.7</v>
       </c>
-      <c r="I276" s="64">
+      <c r="I276" s="45">
         <v>0.75</v>
       </c>
-      <c r="J276" s="65"/>
-      <c r="K276" s="49"/>
-      <c r="L276" s="49"/>
+      <c r="J276" s="45"/>
+      <c r="K276" s="46"/>
+      <c r="L276" s="44"/>
+      <c r="M276" s="44"/>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A277" s="58" t="s">
+      <c r="A277" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="B277" s="59">
+      <c r="B277" s="45">
         <v>424</v>
       </c>
-      <c r="C277" s="60">
+      <c r="C277" s="45">
         <v>16</v>
       </c>
-      <c r="D277" s="60">
+      <c r="D277" s="45">
         <v>9</v>
       </c>
-      <c r="E277" s="61">
+      <c r="E277" s="45">
         <v>39</v>
       </c>
-      <c r="F277" s="61">
+      <c r="F277" s="45">
         <v>29</v>
       </c>
-      <c r="G277" s="62">
-        <v>0</v>
-      </c>
-      <c r="H277" s="63">
+      <c r="G277" s="45">
+        <v>0</v>
+      </c>
+      <c r="H277" s="45">
         <v>32</v>
       </c>
-      <c r="I277" s="64">
+      <c r="I277" s="45">
         <v>0.15</v>
       </c>
-      <c r="J277" s="65"/>
-      <c r="K277" s="49"/>
-      <c r="L277" s="49" t="s">
+      <c r="J277" s="45"/>
+      <c r="K277" s="46"/>
+      <c r="L277" s="44" t="s">
         <v>304</v>
       </c>
+      <c r="M277" s="44"/>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A278" s="58" t="s">
+      <c r="A278" s="44" t="s">
         <v>305</v>
       </c>
-      <c r="B278" s="59">
+      <c r="B278" s="45">
         <v>407</v>
       </c>
-      <c r="C278" s="60">
+      <c r="C278" s="45">
         <v>11</v>
       </c>
-      <c r="D278" s="60">
+      <c r="D278" s="45">
         <v>5.7</v>
       </c>
-      <c r="E278" s="61">
+      <c r="E278" s="45">
         <v>57</v>
       </c>
-      <c r="F278" s="61">
+      <c r="F278" s="45">
         <v>37</v>
       </c>
-      <c r="G278" s="62">
-        <v>0</v>
-      </c>
-      <c r="H278" s="63">
+      <c r="G278" s="45">
+        <v>0</v>
+      </c>
+      <c r="H278" s="45">
         <v>19</v>
       </c>
-      <c r="I278" s="64">
+      <c r="I278" s="45">
         <v>0.49</v>
       </c>
-      <c r="J278" s="65"/>
-      <c r="K278" s="57">
+      <c r="J278" s="45"/>
+      <c r="K278" s="46">
         <v>45194</v>
       </c>
-      <c r="L278" s="49" t="s">
+      <c r="L278" s="44" t="s">
         <v>306</v>
       </c>
+      <c r="M278" s="44"/>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A279" s="58" t="s">
+      <c r="A279" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="B279" s="59">
+      <c r="B279" s="45">
         <v>400</v>
       </c>
-      <c r="C279" s="60">
+      <c r="C279" s="45">
         <v>14</v>
       </c>
-      <c r="D279" s="60">
+      <c r="D279" s="45">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E279" s="61">
+      <c r="E279" s="45">
         <v>34</v>
       </c>
-      <c r="F279" s="61">
+      <c r="F279" s="45">
         <v>28</v>
       </c>
-      <c r="G279" s="62">
+      <c r="G279" s="45">
         <v>5.6</v>
       </c>
-      <c r="H279" s="63">
+      <c r="H279" s="45">
         <v>35</v>
       </c>
-      <c r="I279" s="64">
+      <c r="I279" s="45">
         <v>0.1</v>
       </c>
-      <c r="J279" s="65"/>
-      <c r="K279" s="57">
+      <c r="J279" s="45"/>
+      <c r="K279" s="46">
         <v>45188</v>
       </c>
-      <c r="L279" s="49" t="s">
+      <c r="L279" s="44" t="s">
         <v>308</v>
       </c>
+      <c r="M279" s="44"/>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A280" s="58" t="s">
+      <c r="A280" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="B280" s="59">
+      <c r="B280" s="45">
         <v>344</v>
       </c>
-      <c r="C280" s="60">
+      <c r="C280" s="45">
         <v>4.7</v>
       </c>
-      <c r="D280" s="60">
+      <c r="D280" s="45">
         <v>1.2</v>
       </c>
-      <c r="E280" s="61">
+      <c r="E280" s="45">
         <v>54</v>
       </c>
-      <c r="F280" s="61">
+      <c r="F280" s="45">
         <v>30</v>
       </c>
-      <c r="G280" s="62">
-        <v>0</v>
-      </c>
-      <c r="H280" s="63">
+      <c r="G280" s="45">
+        <v>0</v>
+      </c>
+      <c r="H280" s="45">
         <v>19</v>
       </c>
-      <c r="I280" s="64">
+      <c r="I280" s="45">
         <v>0.25</v>
       </c>
-      <c r="J280" s="65"/>
-      <c r="K280" s="58"/>
-      <c r="L280" s="58" t="s">
+      <c r="J280" s="45"/>
+      <c r="K280" s="46"/>
+      <c r="L280" s="44" t="s">
         <v>310</v>
       </c>
+      <c r="M280" s="44"/>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A281" s="58" t="s">
+      <c r="A281" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="B281" s="59">
+      <c r="B281" s="45">
         <v>187</v>
       </c>
-      <c r="C281" s="60">
+      <c r="C281" s="45">
         <v>9.5</v>
       </c>
-      <c r="D281" s="60">
-        <v>0</v>
-      </c>
-      <c r="E281" s="61">
-        <v>0</v>
-      </c>
-      <c r="F281" s="61">
-        <v>0</v>
-      </c>
-      <c r="G281" s="62">
-        <v>0</v>
-      </c>
-      <c r="H281" s="63">
+      <c r="D281" s="45">
+        <v>0</v>
+      </c>
+      <c r="E281" s="45">
+        <v>0</v>
+      </c>
+      <c r="F281" s="45">
+        <v>0</v>
+      </c>
+      <c r="G281" s="45">
+        <v>0</v>
+      </c>
+      <c r="H281" s="45">
         <v>25.4</v>
       </c>
-      <c r="I281" s="64">
-        <v>0</v>
-      </c>
-      <c r="J281" s="65"/>
-      <c r="K281" s="66">
+      <c r="I281" s="45">
+        <v>0</v>
+      </c>
+      <c r="J281" s="45"/>
+      <c r="K281" s="46">
         <v>45201</v>
       </c>
-      <c r="L281" s="58" t="s">
+      <c r="L281" s="44" t="s">
         <v>312</v>
       </c>
+      <c r="M281" s="44"/>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A282" s="58" t="s">
+      <c r="A282" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="B282" s="59">
+      <c r="B282" s="45">
         <v>151</v>
       </c>
-      <c r="C282" s="60">
+      <c r="C282" s="45">
         <v>3.6</v>
       </c>
-      <c r="D282" s="60">
+      <c r="D282" s="45">
         <v>1.7</v>
       </c>
-      <c r="E282" s="61">
+      <c r="E282" s="45">
         <v>0.3</v>
       </c>
-      <c r="F282" s="61">
+      <c r="F282" s="45">
         <v>0.3</v>
       </c>
-      <c r="G282" s="62">
-        <v>0</v>
-      </c>
-      <c r="H282" s="63">
+      <c r="G282" s="45">
+        <v>0</v>
+      </c>
+      <c r="H282" s="45">
         <v>32</v>
       </c>
-      <c r="I282" s="64">
+      <c r="I282" s="45">
         <v>3.8</v>
       </c>
-      <c r="J282" s="65"/>
-      <c r="K282" s="66"/>
-      <c r="L282" s="58" t="s">
+      <c r="J282" s="45"/>
+      <c r="K282" s="46"/>
+      <c r="L282" s="44" t="s">
         <v>313</v>
       </c>
+      <c r="M282" s="44"/>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A283" s="58" t="s">
+      <c r="A283" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="B283" s="59">
+      <c r="B283" s="45">
         <v>639</v>
       </c>
-      <c r="C283" s="60">
+      <c r="C283" s="45">
         <v>53</v>
       </c>
-      <c r="D283" s="60">
+      <c r="D283" s="45">
         <v>9.5</v>
       </c>
-      <c r="E283" s="61">
+      <c r="E283" s="45">
         <v>10</v>
       </c>
-      <c r="F283" s="61">
+      <c r="F283" s="45">
         <v>6</v>
       </c>
-      <c r="G283" s="62">
+      <c r="G283" s="45">
         <v>7</v>
       </c>
-      <c r="H283" s="63">
+      <c r="H283" s="45">
         <v>27</v>
       </c>
-      <c r="I283" s="64">
-        <v>0</v>
-      </c>
-      <c r="J283" s="65"/>
-      <c r="K283" s="58"/>
-      <c r="L283" s="58"/>
+      <c r="I283" s="45">
+        <v>0</v>
+      </c>
+      <c r="J283" s="45"/>
+      <c r="K283" s="46"/>
+      <c r="L283" s="44"/>
+      <c r="M283" s="44"/>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A284" s="58" t="s">
+      <c r="A284" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="B284" s="59">
+      <c r="B284" s="45">
         <v>130</v>
       </c>
-      <c r="C284" s="60">
+      <c r="C284" s="45">
         <v>1.3</v>
       </c>
-      <c r="D284" s="60">
+      <c r="D284" s="45">
         <v>0.6</v>
       </c>
-      <c r="E284" s="61">
+      <c r="E284" s="45">
         <v>1.85</v>
       </c>
-      <c r="F284" s="61">
+      <c r="F284" s="45">
         <v>1.64</v>
       </c>
-      <c r="G284" s="62">
-        <v>0</v>
-      </c>
-      <c r="H284" s="63">
+      <c r="G284" s="45">
+        <v>0</v>
+      </c>
+      <c r="H284" s="45">
         <v>21</v>
       </c>
-      <c r="I284" s="64">
+      <c r="I284" s="45">
         <v>0.65</v>
       </c>
-      <c r="J284" s="65">
+      <c r="J284" s="45">
         <v>0.95</v>
       </c>
-      <c r="K284" s="66">
+      <c r="K284" s="46">
         <v>45176</v>
       </c>
-      <c r="L284" s="58"/>
+      <c r="L284" s="44"/>
+      <c r="M284" s="44"/>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A285" s="58" t="s">
+      <c r="A285" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="B285" s="59">
+      <c r="B285" s="45">
         <v>119</v>
       </c>
-      <c r="C285" s="60">
+      <c r="C285" s="45">
         <v>2.6</v>
       </c>
-      <c r="D285" s="60">
+      <c r="D285" s="45">
         <v>0.9</v>
       </c>
-      <c r="E285" s="61">
-        <v>0</v>
-      </c>
-      <c r="F285" s="61">
-        <v>0</v>
-      </c>
-      <c r="G285" s="62">
-        <v>0</v>
-      </c>
-      <c r="H285" s="63">
+      <c r="E285" s="45">
+        <v>0</v>
+      </c>
+      <c r="F285" s="45">
+        <v>0</v>
+      </c>
+      <c r="G285" s="45">
+        <v>0</v>
+      </c>
+      <c r="H285" s="45">
         <v>22.3</v>
       </c>
-      <c r="I285" s="64">
+      <c r="I285" s="45">
         <v>0.06</v>
       </c>
-      <c r="J285" s="65"/>
-      <c r="K285" s="66">
+      <c r="J285" s="45"/>
+      <c r="K285" s="46">
         <v>45180</v>
       </c>
-      <c r="L285" s="58"/>
+      <c r="L285" s="44"/>
+      <c r="M285" s="44"/>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A286" s="58" t="s">
+      <c r="A286" s="44" t="s">
         <v>317</v>
       </c>
-      <c r="B286" s="59">
+      <c r="B286" s="45">
         <v>626</v>
       </c>
-      <c r="C286" s="60">
+      <c r="C286" s="45">
         <v>54</v>
       </c>
-      <c r="D286" s="60">
+      <c r="D286" s="45">
         <v>36</v>
       </c>
-      <c r="E286" s="61">
+      <c r="E286" s="45">
         <v>16</v>
       </c>
-      <c r="F286" s="61">
+      <c r="F286" s="45">
         <v>1.5</v>
       </c>
-      <c r="G286" s="62">
-        <v>0</v>
-      </c>
-      <c r="H286" s="63">
+      <c r="G286" s="45">
+        <v>0</v>
+      </c>
+      <c r="H286" s="45">
         <v>11</v>
       </c>
-      <c r="I286" s="64">
-        <v>0</v>
-      </c>
-      <c r="J286" s="65"/>
-      <c r="K286" s="66">
+      <c r="I286" s="45">
+        <v>0</v>
+      </c>
+      <c r="J286" s="45"/>
+      <c r="K286" s="46">
         <v>45215</v>
       </c>
-      <c r="L286" s="58"/>
+      <c r="L286" s="44"/>
+      <c r="M286" s="44"/>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A287" s="58" t="s">
+      <c r="A287" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="B287" s="59">
+      <c r="B287" s="45">
         <v>386</v>
       </c>
-      <c r="C287" s="60">
+      <c r="C287" s="45">
         <v>1.9</v>
       </c>
-      <c r="D287" s="60">
+      <c r="D287" s="45">
         <v>0.9</v>
       </c>
-      <c r="E287" s="61">
+      <c r="E287" s="45">
         <v>84</v>
       </c>
-      <c r="F287" s="61">
+      <c r="F287" s="45">
         <v>17</v>
       </c>
-      <c r="G287" s="62">
+      <c r="G287" s="45">
         <v>3.8</v>
       </c>
-      <c r="H287" s="63">
+      <c r="H287" s="45">
         <v>6.3</v>
       </c>
-      <c r="I287" s="64">
+      <c r="I287" s="45">
         <v>0.65</v>
       </c>
-      <c r="J287" s="65">
+      <c r="J287" s="45">
         <v>0.94499999999999995</v>
       </c>
-      <c r="K287" s="58"/>
-      <c r="L287" s="58"/>
+      <c r="K287" s="46"/>
+      <c r="L287" s="44"/>
+      <c r="M287" s="44"/>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A288" s="58" t="s">
+      <c r="A288" s="44" t="s">
         <v>319</v>
       </c>
-      <c r="B288" s="59">
+      <c r="B288" s="45">
         <v>245</v>
       </c>
-      <c r="C288" s="60">
+      <c r="C288" s="45">
         <v>15</v>
       </c>
-      <c r="D288" s="60">
+      <c r="D288" s="45">
         <v>10</v>
       </c>
-      <c r="E288" s="61">
+      <c r="E288" s="45">
         <v>26</v>
       </c>
-      <c r="F288" s="61">
+      <c r="F288" s="45">
         <v>17</v>
       </c>
-      <c r="G288" s="62">
-        <v>0</v>
-      </c>
-      <c r="H288" s="63">
+      <c r="G288" s="45">
+        <v>0</v>
+      </c>
+      <c r="H288" s="45">
         <v>2.7</v>
       </c>
-      <c r="I288" s="64">
+      <c r="I288" s="45">
         <v>0.2</v>
       </c>
-      <c r="J288" s="65"/>
-      <c r="K288" s="66">
+      <c r="J288" s="45"/>
+      <c r="K288" s="46">
         <v>45543</v>
       </c>
-      <c r="L288" s="58" t="s">
+      <c r="L288" s="44" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A289" s="58" t="s">
+      <c r="M288" s="44"/>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A289" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="B289" s="59">
+      <c r="B289" s="45">
         <v>484</v>
       </c>
-      <c r="C289" s="60">
+      <c r="C289" s="45">
         <v>22.42</v>
       </c>
-      <c r="D289" s="60">
-        <v>0</v>
-      </c>
-      <c r="E289" s="61">
+      <c r="D289" s="45">
+        <v>0</v>
+      </c>
+      <c r="E289" s="45">
         <v>64.48</v>
       </c>
-      <c r="F289" s="61">
+      <c r="F289" s="45">
         <v>20</v>
       </c>
-      <c r="G289" s="62">
+      <c r="G289" s="45">
         <v>2.7</v>
       </c>
-      <c r="H289" s="63">
+      <c r="H289" s="45">
         <v>6</v>
       </c>
-      <c r="I289" s="64">
-        <v>0</v>
-      </c>
-      <c r="J289" s="65"/>
-      <c r="K289" s="66">
+      <c r="I289" s="45">
+        <v>0</v>
+      </c>
+      <c r="J289" s="45"/>
+      <c r="K289" s="46">
         <v>45184</v>
       </c>
-      <c r="L289" s="58"/>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A290" s="58" t="s">
+      <c r="L289" s="44"/>
+      <c r="M289" s="44"/>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A290" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="B290" s="59">
+      <c r="B290" s="45">
         <v>93</v>
       </c>
-      <c r="C290" s="60">
+      <c r="C290" s="45">
         <v>5</v>
       </c>
-      <c r="D290" s="60">
+      <c r="D290" s="45">
         <v>3.6</v>
       </c>
-      <c r="E290" s="61">
+      <c r="E290" s="45">
         <v>3</v>
       </c>
-      <c r="F290" s="61">
+      <c r="F290" s="45">
         <v>3</v>
       </c>
-      <c r="G290" s="62">
-        <v>0</v>
-      </c>
-      <c r="H290" s="63">
+      <c r="G290" s="45">
+        <v>0</v>
+      </c>
+      <c r="H290" s="45">
         <v>9</v>
       </c>
-      <c r="I290" s="64">
+      <c r="I290" s="45">
         <v>0.1</v>
       </c>
-      <c r="J290" s="65">
+      <c r="J290" s="45">
         <v>0.92700000000000005</v>
       </c>
-      <c r="K290" s="66">
+      <c r="K290" s="46">
         <v>45178</v>
       </c>
-      <c r="L290" s="58" t="s">
+      <c r="L290" s="44" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A291" s="58" t="s">
+      <c r="M290" s="44"/>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A291" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="B291" s="59">
+      <c r="B291" s="45">
         <v>63</v>
       </c>
-      <c r="C291" s="60">
+      <c r="C291" s="45">
         <v>0.2</v>
       </c>
-      <c r="D291" s="60">
-        <v>0</v>
-      </c>
-      <c r="E291" s="61">
+      <c r="D291" s="45">
+        <v>0</v>
+      </c>
+      <c r="E291" s="45">
         <v>14.2</v>
       </c>
-      <c r="F291" s="61">
+      <c r="F291" s="45">
         <v>14.2</v>
       </c>
-      <c r="G291" s="62">
+      <c r="G291" s="45">
         <v>2</v>
       </c>
-      <c r="H291" s="63">
+      <c r="H291" s="45">
         <v>0.9</v>
       </c>
-      <c r="I291" s="64">
-        <v>0</v>
-      </c>
-      <c r="J291" s="65"/>
-      <c r="K291" s="66">
+      <c r="I291" s="45">
+        <v>0</v>
+      </c>
+      <c r="J291" s="45"/>
+      <c r="K291" s="46">
         <v>45194</v>
       </c>
-      <c r="L291" s="58" t="s">
+      <c r="L291" s="44" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A292" s="58" t="s">
+      <c r="M291" s="44"/>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A292" s="44" t="s">
         <v>326</v>
       </c>
-      <c r="B292" s="59">
+      <c r="B292" s="45">
         <v>295</v>
       </c>
-      <c r="C292" s="60">
+      <c r="C292" s="45">
         <v>11.4</v>
       </c>
-      <c r="D292" s="60">
+      <c r="D292" s="45">
         <v>1.42</v>
       </c>
-      <c r="E292" s="61">
+      <c r="E292" s="45">
         <v>41.32</v>
       </c>
-      <c r="F292" s="61">
+      <c r="F292" s="45">
         <v>2.36</v>
       </c>
-      <c r="G292" s="62">
+      <c r="G292" s="45">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H292" s="63">
+      <c r="H292" s="45">
         <v>6.61</v>
       </c>
-      <c r="I292" s="64">
+      <c r="I292" s="45">
         <v>0.7</v>
       </c>
-      <c r="J292" s="65"/>
-      <c r="K292" s="66">
+      <c r="J292" s="45"/>
+      <c r="K292" s="46">
         <v>45201</v>
       </c>
-      <c r="L292" s="58"/>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A293" s="58" t="s">
+      <c r="L292" s="44"/>
+      <c r="M292" s="44"/>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A293" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="B293" s="59">
+      <c r="B293" s="45">
         <v>377</v>
       </c>
-      <c r="C293" s="60">
+      <c r="C293" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D293" s="60">
+      <c r="D293" s="45">
         <v>0.3</v>
       </c>
-      <c r="E293" s="61">
+      <c r="E293" s="45">
         <v>83</v>
       </c>
-      <c r="F293" s="61">
+      <c r="F293" s="45">
         <v>0.1</v>
       </c>
-      <c r="G293" s="62">
+      <c r="G293" s="45">
         <v>2.8</v>
       </c>
-      <c r="H293" s="63">
+      <c r="H293" s="45">
         <v>7.3</v>
       </c>
-      <c r="I293" s="64">
+      <c r="I293" s="45">
         <v>0.8</v>
       </c>
-      <c r="J293" s="65">
+      <c r="J293" s="45">
         <v>1.26</v>
       </c>
-      <c r="K293" s="66">
+      <c r="K293" s="46">
         <v>45179</v>
       </c>
-      <c r="L293" s="58" t="s">
+      <c r="L293" s="44" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A294" s="58" t="s">
+      <c r="M293" s="44"/>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A294" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="B294" s="59">
+      <c r="B294" s="45">
         <v>24</v>
       </c>
-      <c r="C294" s="60">
-        <v>0</v>
-      </c>
-      <c r="D294" s="60">
-        <v>0</v>
-      </c>
-      <c r="E294" s="61">
+      <c r="C294" s="45">
+        <v>0</v>
+      </c>
+      <c r="D294" s="45">
+        <v>0</v>
+      </c>
+      <c r="E294" s="45">
         <v>5.9</v>
       </c>
-      <c r="F294" s="61">
+      <c r="F294" s="45">
         <v>3.9</v>
       </c>
-      <c r="G294" s="62">
-        <v>0</v>
-      </c>
-      <c r="H294" s="63">
-        <v>0</v>
-      </c>
-      <c r="I294" s="64">
+      <c r="G294" s="45">
+        <v>0</v>
+      </c>
+      <c r="H294" s="45">
+        <v>0</v>
+      </c>
+      <c r="I294" s="45">
         <v>0.13</v>
       </c>
-      <c r="J294" s="65">
+      <c r="J294" s="45">
         <v>1.18</v>
       </c>
-      <c r="K294" s="66">
+      <c r="K294" s="46">
         <v>45179</v>
       </c>
-      <c r="L294" s="58"/>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A295" s="58" t="s">
+      <c r="L294" s="44"/>
+      <c r="M294" s="44"/>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A295" s="44" t="s">
         <v>330</v>
       </c>
-      <c r="B295" s="59">
+      <c r="B295" s="45">
         <v>153</v>
       </c>
-      <c r="C295" s="60">
+      <c r="C295" s="45">
         <v>10</v>
       </c>
-      <c r="D295" s="60">
+      <c r="D295" s="45">
         <v>1.56</v>
       </c>
-      <c r="E295" s="61">
+      <c r="E295" s="45">
         <v>1.6</v>
       </c>
-      <c r="F295" s="61">
+      <c r="F295" s="45">
         <v>0.8</v>
       </c>
-      <c r="G295" s="62">
+      <c r="G295" s="45">
         <v>0.2</v>
       </c>
-      <c r="H295" s="63">
+      <c r="H295" s="45">
         <v>11.84</v>
       </c>
-      <c r="I295" s="64">
+      <c r="I295" s="45">
         <v>0.9</v>
       </c>
-      <c r="J295" s="65"/>
-      <c r="K295" s="66">
+      <c r="J295" s="45"/>
+      <c r="K295" s="46">
         <v>45225</v>
       </c>
-      <c r="L295" s="58"/>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A296" s="58" t="s">
+      <c r="L295" s="44"/>
+      <c r="M295" s="44"/>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A296" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="B296" s="59">
+      <c r="B296" s="45">
         <v>161</v>
       </c>
-      <c r="C296" s="60">
+      <c r="C296" s="45">
         <v>4.22</v>
       </c>
-      <c r="D296" s="60">
+      <c r="D296" s="45">
         <v>1.5</v>
       </c>
-      <c r="E296" s="61">
+      <c r="E296" s="45">
         <v>20.29</v>
       </c>
-      <c r="F296" s="61">
+      <c r="F296" s="45">
         <v>1.74</v>
       </c>
-      <c r="G296" s="62">
+      <c r="G296" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H296" s="63">
+      <c r="H296" s="45">
         <v>9.6999999999999993</v>
       </c>
-      <c r="I296" s="64">
+      <c r="I296" s="45">
         <v>0.67</v>
       </c>
-      <c r="J296" s="65"/>
-      <c r="K296" s="66">
+      <c r="J296" s="45"/>
+      <c r="K296" s="46">
         <v>45197</v>
       </c>
-      <c r="L296" s="58"/>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A297" s="58" t="s">
+      <c r="L296" s="44"/>
+      <c r="M296" s="44"/>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A297" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="B297" s="59">
+      <c r="B297" s="45">
         <v>62</v>
       </c>
-      <c r="C297" s="60">
+      <c r="C297" s="45">
         <v>3.5</v>
       </c>
-      <c r="D297" s="60">
+      <c r="D297" s="45">
         <v>0.4</v>
       </c>
-      <c r="E297" s="61">
+      <c r="E297" s="45">
         <v>6.3</v>
       </c>
-      <c r="F297" s="61">
+      <c r="F297" s="45">
         <v>1.2</v>
       </c>
-      <c r="G297" s="62">
+      <c r="G297" s="45">
         <v>1</v>
       </c>
-      <c r="H297" s="63">
+      <c r="H297" s="45">
         <v>0.7</v>
       </c>
-      <c r="I297" s="64">
+      <c r="I297" s="45">
         <v>0.12</v>
       </c>
-      <c r="J297" s="65"/>
-      <c r="K297" s="66">
+      <c r="J297" s="45"/>
+      <c r="K297" s="46">
         <v>45543</v>
       </c>
-      <c r="L297" s="58"/>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A298" s="58" t="s">
+      <c r="L297" s="44"/>
+      <c r="M297" s="44"/>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A298" s="44" t="s">
         <v>333</v>
       </c>
-      <c r="B298" s="59">
+      <c r="B298" s="45">
         <v>232</v>
       </c>
-      <c r="C298" s="60">
+      <c r="C298" s="45">
         <v>18</v>
       </c>
-      <c r="D298" s="60">
-        <v>0</v>
-      </c>
-      <c r="E298" s="61">
+      <c r="D298" s="45">
+        <v>0</v>
+      </c>
+      <c r="E298" s="45">
         <v>0.44</v>
       </c>
-      <c r="F298" s="61">
+      <c r="F298" s="45">
         <v>0.4</v>
       </c>
-      <c r="G298" s="62">
-        <v>0</v>
-      </c>
-      <c r="H298" s="63">
+      <c r="G298" s="45">
+        <v>0</v>
+      </c>
+      <c r="H298" s="45">
         <v>17.100000000000001</v>
       </c>
-      <c r="I298" s="64">
+      <c r="I298" s="45">
         <v>0.5</v>
       </c>
-      <c r="J298" s="65"/>
-      <c r="K298" s="66">
+      <c r="J298" s="45"/>
+      <c r="K298" s="46">
         <v>45184</v>
       </c>
-      <c r="L298" s="58"/>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A299" s="58" t="s">
+      <c r="L298" s="44"/>
+      <c r="M298" s="44"/>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A299" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="B299" s="59">
+      <c r="B299" s="45">
         <v>603</v>
       </c>
-      <c r="C299" s="60">
+      <c r="C299" s="45">
         <v>67</v>
       </c>
-      <c r="D299" s="60">
+      <c r="D299" s="45">
         <v>8.1</v>
       </c>
-      <c r="E299" s="61">
+      <c r="E299" s="45">
         <v>0.5</v>
       </c>
-      <c r="F299" s="61">
+      <c r="F299" s="45">
         <v>0.5</v>
       </c>
-      <c r="G299" s="62">
+      <c r="G299" s="45">
         <v>0.5</v>
       </c>
-      <c r="H299" s="63">
+      <c r="H299" s="45">
         <v>0.8</v>
       </c>
-      <c r="I299" s="64">
+      <c r="I299" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J299" s="65"/>
-      <c r="K299" s="66">
+      <c r="J299" s="45"/>
+      <c r="K299" s="46">
         <v>45222</v>
       </c>
-      <c r="L299" s="58" t="s">
+      <c r="L299" s="44" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A300" s="58" t="s">
+      <c r="M299" s="44"/>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A300" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="B300" s="59">
+      <c r="B300" s="45">
         <v>628</v>
       </c>
-      <c r="C300" s="60">
+      <c r="C300" s="45">
         <v>55.3</v>
       </c>
-      <c r="D300" s="60"/>
-      <c r="E300" s="61">
+      <c r="D300" s="45"/>
+      <c r="E300" s="45">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F300" s="61"/>
-      <c r="G300" s="62">
+      <c r="F300" s="45"/>
+      <c r="G300" s="45">
         <v>12.7</v>
       </c>
-      <c r="H300" s="63">
+      <c r="H300" s="45">
         <v>22</v>
       </c>
-      <c r="I300" s="64"/>
-      <c r="J300" s="65"/>
-      <c r="K300" s="66">
+      <c r="I300" s="45"/>
+      <c r="J300" s="45"/>
+      <c r="K300" s="46">
         <v>45205</v>
       </c>
-      <c r="L300" s="58"/>
-    </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A301" s="58" t="s">
+      <c r="L300" s="44"/>
+      <c r="M300" s="44"/>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A301" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="B301" s="59">
+      <c r="B301" s="45">
         <v>42</v>
       </c>
-      <c r="C301" s="60">
+      <c r="C301" s="45">
         <v>2.1</v>
       </c>
-      <c r="D301" s="60">
+      <c r="D301" s="45">
         <v>0.35</v>
       </c>
-      <c r="E301" s="61">
+      <c r="E301" s="45">
         <v>5.2</v>
       </c>
-      <c r="F301" s="61">
-        <v>0</v>
-      </c>
-      <c r="G301" s="62">
+      <c r="F301" s="45">
+        <v>0</v>
+      </c>
+      <c r="G301" s="45">
         <v>2.8</v>
       </c>
-      <c r="H301" s="63">
+      <c r="H301" s="45">
         <v>1</v>
       </c>
-      <c r="I301" s="64">
-        <v>0</v>
-      </c>
-      <c r="J301" s="65"/>
-      <c r="K301" s="66">
+      <c r="I301" s="45">
+        <v>0</v>
+      </c>
+      <c r="J301" s="45"/>
+      <c r="K301" s="46">
         <v>45537</v>
       </c>
-      <c r="L301" s="58"/>
-    </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A302" s="58" t="s">
+      <c r="L301" s="44"/>
+      <c r="M301" s="44"/>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A302" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="B302" s="59">
+      <c r="B302" s="45">
         <v>125</v>
       </c>
-      <c r="C302" s="60">
+      <c r="C302" s="45">
         <v>3.4</v>
       </c>
-      <c r="D302" s="60">
+      <c r="D302" s="45">
         <v>0.7</v>
       </c>
-      <c r="E302" s="61">
+      <c r="E302" s="45">
         <v>14</v>
       </c>
-      <c r="F302" s="61">
+      <c r="F302" s="45">
         <v>8</v>
       </c>
-      <c r="G302" s="62">
+      <c r="G302" s="45">
         <v>0.5</v>
       </c>
-      <c r="H302" s="63">
+      <c r="H302" s="45">
         <v>9.4</v>
       </c>
-      <c r="I302" s="64">
+      <c r="I302" s="45">
         <v>0.2</v>
       </c>
-      <c r="J302" s="65"/>
-      <c r="K302" s="66">
+      <c r="J302" s="45"/>
+      <c r="K302" s="46">
         <v>45197</v>
       </c>
-      <c r="L302" s="58" t="s">
+      <c r="L302" s="44" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A303" s="58" t="s">
+      <c r="M302" s="44"/>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A303" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="B303" s="59">
+      <c r="B303" s="45">
         <v>304</v>
       </c>
-      <c r="C303" s="60">
-        <v>0</v>
-      </c>
-      <c r="D303" s="60">
-        <v>0</v>
-      </c>
-      <c r="E303" s="61">
+      <c r="C303" s="45">
+        <v>0</v>
+      </c>
+      <c r="D303" s="45">
+        <v>0</v>
+      </c>
+      <c r="E303" s="45">
         <v>82</v>
       </c>
-      <c r="F303" s="61">
+      <c r="F303" s="45">
         <v>82</v>
       </c>
-      <c r="G303" s="62">
+      <c r="G303" s="45">
         <v>0.2</v>
       </c>
-      <c r="H303" s="63">
+      <c r="H303" s="45">
         <v>0.3</v>
       </c>
-      <c r="I303" s="64">
-        <v>0</v>
-      </c>
-      <c r="J303" s="65"/>
-      <c r="K303" s="58"/>
-      <c r="L303" s="58"/>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A304" s="58" t="s">
+      <c r="I303" s="45">
+        <v>0</v>
+      </c>
+      <c r="J303" s="45"/>
+      <c r="K303" s="46"/>
+      <c r="L303" s="44"/>
+      <c r="M303" s="44"/>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A304" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="B304" s="59">
+      <c r="B304" s="45">
         <v>288</v>
       </c>
-      <c r="C304" s="60">
+      <c r="C304" s="45">
         <v>25</v>
       </c>
-      <c r="D304" s="60">
-        <v>0</v>
-      </c>
-      <c r="E304" s="61">
+      <c r="D304" s="45">
+        <v>0</v>
+      </c>
+      <c r="E304" s="45">
         <v>1.5</v>
       </c>
-      <c r="F304" s="61">
-        <v>0</v>
-      </c>
-      <c r="G304" s="62">
-        <v>0</v>
-      </c>
-      <c r="H304" s="63">
+      <c r="F304" s="45">
+        <v>0</v>
+      </c>
+      <c r="G304" s="45">
+        <v>0</v>
+      </c>
+      <c r="H304" s="45">
         <v>15.7</v>
       </c>
-      <c r="I304" s="64">
+      <c r="I304" s="45">
         <v>0.4</v>
       </c>
-      <c r="J304" s="65"/>
-      <c r="K304" s="66">
+      <c r="J304" s="45"/>
+      <c r="K304" s="46">
         <v>45540</v>
       </c>
-      <c r="L304" s="58"/>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A305" s="58" t="s">
+      <c r="L304" s="44"/>
+      <c r="M304" s="44"/>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A305" s="44" t="s">
         <v>339</v>
       </c>
-      <c r="B305" s="59">
+      <c r="B305" s="45">
         <v>238</v>
       </c>
-      <c r="C305" s="60">
+      <c r="C305" s="45">
         <v>18</v>
       </c>
-      <c r="D305" s="60">
+      <c r="D305" s="45">
         <v>13</v>
       </c>
-      <c r="E305" s="61">
+      <c r="E305" s="45">
         <v>2</v>
       </c>
-      <c r="F305" s="61">
+      <c r="F305" s="45">
         <v>1</v>
       </c>
-      <c r="G305" s="62">
-        <v>0</v>
-      </c>
-      <c r="H305" s="63">
+      <c r="G305" s="45">
+        <v>0</v>
+      </c>
+      <c r="H305" s="45">
         <v>17</v>
       </c>
-      <c r="I305" s="64">
+      <c r="I305" s="45">
         <v>0.7</v>
       </c>
-      <c r="J305" s="65"/>
-      <c r="K305" s="58"/>
-      <c r="L305" s="58"/>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A306" s="58" t="s">
+      <c r="J305" s="45"/>
+      <c r="K305" s="46"/>
+      <c r="L305" s="44"/>
+      <c r="M305" s="44"/>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A306" s="44" t="s">
         <v>340</v>
       </c>
-      <c r="B306" s="59">
+      <c r="B306" s="45">
         <v>462</v>
       </c>
-      <c r="C306" s="60">
+      <c r="C306" s="45">
         <v>19</v>
       </c>
-      <c r="D306" s="60">
+      <c r="D306" s="45">
         <v>5</v>
       </c>
-      <c r="E306" s="61">
+      <c r="E306" s="45">
         <v>61</v>
       </c>
-      <c r="F306" s="61">
+      <c r="F306" s="45">
         <v>28</v>
       </c>
-      <c r="G306" s="62">
+      <c r="G306" s="45">
         <v>6</v>
       </c>
-      <c r="H306" s="63">
+      <c r="H306" s="45">
         <v>8.5</v>
       </c>
-      <c r="I306" s="64">
+      <c r="I306" s="45">
         <v>0.4</v>
       </c>
-      <c r="J306" s="65"/>
-      <c r="K306" s="66">
+      <c r="J306" s="45"/>
+      <c r="K306" s="46">
         <v>45189</v>
       </c>
-      <c r="L306" s="58"/>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A307" s="58" t="s">
+      <c r="L306" s="44"/>
+      <c r="M306" s="44"/>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A307" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="B307" s="59">
+      <c r="B307" s="45">
         <v>90</v>
       </c>
-      <c r="C307" s="60">
+      <c r="C307" s="45">
         <v>1.8</v>
       </c>
-      <c r="D307" s="60">
+      <c r="D307" s="45">
         <v>0.6</v>
       </c>
-      <c r="E307" s="61">
-        <v>0</v>
-      </c>
-      <c r="F307" s="61">
-        <v>0</v>
-      </c>
-      <c r="G307" s="62">
-        <v>0</v>
-      </c>
-      <c r="H307" s="63">
+      <c r="E307" s="45">
+        <v>0</v>
+      </c>
+      <c r="F307" s="45">
+        <v>0</v>
+      </c>
+      <c r="G307" s="45">
+        <v>0</v>
+      </c>
+      <c r="H307" s="45">
         <v>17.36</v>
       </c>
-      <c r="I307" s="64">
+      <c r="I307" s="45">
         <v>0.1</v>
       </c>
-      <c r="J307" s="65"/>
-      <c r="K307" s="58"/>
-      <c r="L307" s="58"/>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A308" s="58" t="s">
+      <c r="J307" s="45"/>
+      <c r="K307" s="46"/>
+      <c r="L307" s="44"/>
+      <c r="M307" s="44"/>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A308" s="44" t="s">
         <v>342</v>
       </c>
-      <c r="B308" s="59">
+      <c r="B308" s="45">
         <v>449</v>
       </c>
-      <c r="C308" s="60">
+      <c r="C308" s="45">
         <v>17</v>
       </c>
-      <c r="D308" s="60">
+      <c r="D308" s="45">
         <v>2.4</v>
       </c>
-      <c r="E308" s="61">
+      <c r="E308" s="45">
         <v>62.1</v>
       </c>
-      <c r="F308" s="61">
+      <c r="F308" s="45">
         <v>1.8</v>
       </c>
-      <c r="G308" s="62">
+      <c r="G308" s="45">
         <v>3.9</v>
       </c>
-      <c r="H308" s="63">
+      <c r="H308" s="45">
         <v>9.9</v>
       </c>
-      <c r="I308" s="64">
+      <c r="I308" s="45">
         <v>3</v>
       </c>
-      <c r="J308" s="65">
+      <c r="J308" s="45">
         <v>0.97199999999999998</v>
       </c>
-      <c r="K308" s="58"/>
-      <c r="L308" s="58" t="s">
+      <c r="K308" s="46"/>
+      <c r="L308" s="44" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A309" s="58" t="s">
+      <c r="M308" s="44"/>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A309" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="B309" s="59">
+      <c r="B309" s="45">
         <v>539</v>
       </c>
-      <c r="C309" s="60">
+      <c r="C309" s="45">
         <v>30.9</v>
       </c>
-      <c r="D309" s="60">
+      <c r="D309" s="45">
         <v>10.6</v>
       </c>
-      <c r="E309" s="61">
+      <c r="E309" s="45">
         <v>55.5</v>
       </c>
-      <c r="F309" s="61">
+      <c r="F309" s="45">
         <v>56.3</v>
       </c>
-      <c r="G309" s="62">
-        <v>0</v>
-      </c>
-      <c r="H309" s="63">
+      <c r="G309" s="45">
+        <v>0</v>
+      </c>
+      <c r="H309" s="45">
         <v>6.3</v>
       </c>
-      <c r="I309" s="64">
+      <c r="I309" s="45">
         <v>0.107</v>
       </c>
-      <c r="J309" s="65"/>
-      <c r="K309" s="58"/>
-      <c r="L309" s="58"/>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A310" s="58" t="s">
+      <c r="J309" s="45"/>
+      <c r="K309" s="46"/>
+      <c r="L309" s="44"/>
+      <c r="M309" s="44"/>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A310" s="44" t="s">
         <v>345</v>
       </c>
-      <c r="B310" s="59">
+      <c r="B310" s="45">
         <v>884</v>
       </c>
-      <c r="C310" s="60">
+      <c r="C310" s="45">
         <v>100</v>
       </c>
-      <c r="D310" s="60">
-        <v>0</v>
-      </c>
-      <c r="E310" s="61">
-        <v>0</v>
-      </c>
-      <c r="F310" s="61">
-        <v>0</v>
-      </c>
-      <c r="G310" s="62">
-        <v>0</v>
-      </c>
-      <c r="H310" s="63">
-        <v>0</v>
-      </c>
-      <c r="I310" s="64">
-        <v>0</v>
-      </c>
-      <c r="J310" s="65"/>
-      <c r="K310" s="66">
+      <c r="D310" s="45">
+        <v>0</v>
+      </c>
+      <c r="E310" s="45">
+        <v>0</v>
+      </c>
+      <c r="F310" s="45">
+        <v>0</v>
+      </c>
+      <c r="G310" s="45">
+        <v>0</v>
+      </c>
+      <c r="H310" s="45">
+        <v>0</v>
+      </c>
+      <c r="I310" s="45">
+        <v>0</v>
+      </c>
+      <c r="J310" s="45"/>
+      <c r="K310" s="46">
         <v>45197</v>
       </c>
-      <c r="L310" s="58" t="s">
+      <c r="L310" s="44" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A311" s="58" t="s">
+      <c r="M310" s="44"/>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A311" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="B311" s="59">
+      <c r="B311" s="45">
         <v>268</v>
       </c>
-      <c r="C311" s="60">
+      <c r="C311" s="45">
         <v>0.5</v>
       </c>
-      <c r="D311" s="60">
-        <v>0</v>
-      </c>
-      <c r="E311" s="61">
+      <c r="D311" s="45">
+        <v>0</v>
+      </c>
+      <c r="E311" s="45">
         <v>59.5</v>
       </c>
-      <c r="F311" s="61">
-        <v>0</v>
-      </c>
-      <c r="G311" s="62">
-        <v>0</v>
-      </c>
-      <c r="H311" s="63">
+      <c r="F311" s="45">
+        <v>0</v>
+      </c>
+      <c r="G311" s="45">
+        <v>0</v>
+      </c>
+      <c r="H311" s="45">
         <v>8.1</v>
       </c>
-      <c r="I311" s="64">
+      <c r="I311" s="45">
         <v>0.5</v>
       </c>
-      <c r="J311" s="65"/>
-      <c r="K311" s="66">
+      <c r="J311" s="45"/>
+      <c r="K311" s="46">
         <v>45229</v>
       </c>
-      <c r="L311" s="58"/>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A312" s="58" t="s">
+      <c r="L311" s="44"/>
+      <c r="M311" s="44"/>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A312" s="44" t="s">
         <v>348</v>
       </c>
-      <c r="B312" s="59">
+      <c r="B312" s="45">
         <v>274</v>
       </c>
-      <c r="C312" s="60">
+      <c r="C312" s="45">
         <v>3.8</v>
       </c>
-      <c r="D312" s="60">
+      <c r="D312" s="45">
         <v>0.5</v>
       </c>
-      <c r="E312" s="61">
+      <c r="E312" s="45">
         <v>49.7</v>
       </c>
-      <c r="F312" s="61">
+      <c r="F312" s="45">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G312" s="62">
+      <c r="G312" s="45">
         <v>2.9</v>
       </c>
-      <c r="H312" s="63">
+      <c r="H312" s="45">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I312" s="64">
+      <c r="I312" s="45">
         <v>1.3</v>
       </c>
-      <c r="J312" s="65"/>
-      <c r="K312" s="66">
+      <c r="J312" s="45"/>
+      <c r="K312" s="46">
         <v>45222</v>
       </c>
-      <c r="L312" s="58" t="s">
+      <c r="L312" s="44" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A313" s="58" t="s">
+      <c r="M312" s="44"/>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A313" s="44" t="s">
         <v>350</v>
       </c>
-      <c r="B313" s="59">
+      <c r="B313" s="45">
         <v>371</v>
       </c>
-      <c r="C313" s="60">
+      <c r="C313" s="45">
         <v>1.5</v>
       </c>
-      <c r="D313" s="60">
+      <c r="D313" s="45">
         <v>0.2</v>
       </c>
-      <c r="E313" s="61">
+      <c r="E313" s="45">
         <v>74.67</v>
       </c>
-      <c r="F313" s="61">
+      <c r="F313" s="45">
         <v>2.67</v>
       </c>
-      <c r="G313" s="62">
+      <c r="G313" s="45">
         <v>3.2</v>
       </c>
-      <c r="H313" s="63">
+      <c r="H313" s="45">
         <v>13.04</v>
       </c>
-      <c r="I313" s="64">
+      <c r="I313" s="45">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="J313" s="65"/>
-      <c r="K313" s="58"/>
-      <c r="L313" s="58"/>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A314" s="58" t="s">
+      <c r="J313" s="45"/>
+      <c r="K313" s="46"/>
+      <c r="L313" s="44"/>
+      <c r="M313" s="44"/>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A314" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="B314" s="59"/>
-      <c r="C314" s="60"/>
-      <c r="D314" s="60"/>
-      <c r="E314" s="61"/>
-      <c r="F314" s="61"/>
-      <c r="G314" s="62"/>
-      <c r="H314" s="63"/>
-      <c r="I314" s="64"/>
-      <c r="J314" s="65"/>
-      <c r="K314" s="58"/>
-      <c r="L314" s="58"/>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A315" s="58" t="s">
+      <c r="B314" s="45"/>
+      <c r="C314" s="45"/>
+      <c r="D314" s="45"/>
+      <c r="E314" s="45"/>
+      <c r="F314" s="45"/>
+      <c r="G314" s="45"/>
+      <c r="H314" s="45"/>
+      <c r="I314" s="45"/>
+      <c r="J314" s="45"/>
+      <c r="K314" s="46"/>
+      <c r="L314" s="44"/>
+      <c r="M314" s="44"/>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A315" s="44" t="s">
         <v>352</v>
       </c>
-      <c r="B315" s="59">
+      <c r="B315" s="45">
         <v>548</v>
       </c>
-      <c r="C315" s="60">
+      <c r="C315" s="45">
         <v>29</v>
       </c>
-      <c r="D315" s="60">
+      <c r="D315" s="45">
         <v>15</v>
       </c>
-      <c r="E315" s="61">
+      <c r="E315" s="45">
         <v>56</v>
       </c>
-      <c r="F315" s="61">
+      <c r="F315" s="45">
         <v>4.2</v>
       </c>
-      <c r="G315" s="62">
-        <v>0</v>
-      </c>
-      <c r="H315" s="63">
+      <c r="G315" s="45">
+        <v>0</v>
+      </c>
+      <c r="H315" s="45">
         <v>16</v>
       </c>
-      <c r="I315" s="64">
+      <c r="I315" s="45">
         <v>0.01</v>
       </c>
-      <c r="J315" s="65"/>
-      <c r="K315" s="66">
+      <c r="J315" s="45"/>
+      <c r="K315" s="46">
         <v>45538</v>
       </c>
-      <c r="L315" s="58"/>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A316" s="58" t="s">
+      <c r="L315" s="44"/>
+      <c r="M315" s="44"/>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A316" s="44" t="s">
         <v>353</v>
       </c>
-      <c r="B316" s="59">
+      <c r="B316" s="45">
         <v>545</v>
       </c>
-      <c r="C316" s="60">
+      <c r="C316" s="45">
         <v>5</v>
       </c>
-      <c r="D316" s="60">
+      <c r="D316" s="45">
         <v>0.7</v>
       </c>
-      <c r="E316" s="61">
+      <c r="E316" s="45">
         <v>17</v>
       </c>
-      <c r="F316" s="61">
+      <c r="F316" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G316" s="62">
+      <c r="G316" s="45">
         <v>1.4</v>
       </c>
-      <c r="H316" s="63">
+      <c r="H316" s="45">
         <v>3.5</v>
       </c>
-      <c r="I316" s="64">
+      <c r="I316" s="45">
         <v>1.7</v>
       </c>
-      <c r="J316" s="65"/>
-      <c r="K316" s="66">
+      <c r="J316" s="45"/>
+      <c r="K316" s="46">
         <v>45184</v>
       </c>
-      <c r="L316" s="58"/>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A317" s="58" t="s">
+      <c r="L316" s="44"/>
+      <c r="M316" s="44"/>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A317" s="44" t="s">
         <v>354</v>
       </c>
-      <c r="B317" s="59">
+      <c r="B317" s="45">
         <v>660</v>
       </c>
-      <c r="C317" s="60">
+      <c r="C317" s="45">
         <v>30</v>
       </c>
-      <c r="D317" s="60">
+      <c r="D317" s="45">
         <v>14</v>
       </c>
-      <c r="E317" s="61">
+      <c r="E317" s="45">
         <v>73</v>
       </c>
-      <c r="F317" s="61">
+      <c r="F317" s="45">
         <v>2.5</v>
       </c>
-      <c r="G317" s="62">
+      <c r="G317" s="45">
         <v>3.6</v>
       </c>
-      <c r="H317" s="63">
+      <c r="H317" s="45">
         <v>22.57</v>
       </c>
-      <c r="I317" s="64">
+      <c r="I317" s="45">
         <v>1.7</v>
       </c>
-      <c r="J317" s="65"/>
-      <c r="K317" s="66">
+      <c r="J317" s="45"/>
+      <c r="K317" s="46">
         <v>45180</v>
       </c>
-      <c r="L317" s="58"/>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A318" s="58" t="s">
+      <c r="L317" s="44"/>
+      <c r="M317" s="44"/>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A318" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="B318" s="59"/>
-      <c r="C318" s="60"/>
-      <c r="D318" s="60"/>
-      <c r="E318" s="61"/>
-      <c r="F318" s="61"/>
-      <c r="G318" s="62"/>
-      <c r="H318" s="63"/>
-      <c r="I318" s="64"/>
-      <c r="J318" s="65"/>
-      <c r="K318" s="58"/>
-      <c r="L318" s="58"/>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A319" s="58" t="s">
+      <c r="B318" s="45"/>
+      <c r="C318" s="45"/>
+      <c r="D318" s="45"/>
+      <c r="E318" s="45"/>
+      <c r="F318" s="45"/>
+      <c r="G318" s="45"/>
+      <c r="H318" s="45"/>
+      <c r="I318" s="45"/>
+      <c r="J318" s="45"/>
+      <c r="K318" s="46"/>
+      <c r="L318" s="44"/>
+      <c r="M318" s="44"/>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A319" s="44" t="s">
         <v>356</v>
       </c>
-      <c r="B319" s="59">
+      <c r="B319" s="45">
         <v>100</v>
       </c>
-      <c r="C319" s="60">
+      <c r="C319" s="45">
         <v>0.1</v>
       </c>
-      <c r="D319" s="60">
-        <v>0</v>
-      </c>
-      <c r="E319" s="61">
+      <c r="D319" s="45">
+        <v>0</v>
+      </c>
+      <c r="E319" s="45">
         <v>21</v>
       </c>
-      <c r="F319" s="61">
+      <c r="F319" s="45">
         <v>1.7</v>
       </c>
-      <c r="G319" s="62">
+      <c r="G319" s="45">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H319" s="63">
+      <c r="H319" s="45">
         <v>2.48</v>
       </c>
-      <c r="I319" s="64">
+      <c r="I319" s="45">
         <v>0.69</v>
       </c>
-      <c r="J319" s="65"/>
-      <c r="K319" s="66">
+      <c r="J319" s="45"/>
+      <c r="K319" s="46">
         <v>45225</v>
       </c>
-      <c r="L319" s="58"/>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A320" s="58" t="s">
+      <c r="L319" s="44"/>
+      <c r="M319" s="44"/>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A320" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="B320" s="59">
+      <c r="B320" s="45">
         <v>129</v>
       </c>
-      <c r="C320" s="60">
+      <c r="C320" s="45">
         <v>0.9</v>
       </c>
-      <c r="D320" s="60">
-        <v>0</v>
-      </c>
-      <c r="E320" s="61">
-        <v>0</v>
-      </c>
-      <c r="F320" s="61">
-        <v>0</v>
-      </c>
-      <c r="G320" s="62">
-        <v>0</v>
-      </c>
-      <c r="H320" s="63">
+      <c r="D320" s="45">
+        <v>0</v>
+      </c>
+      <c r="E320" s="45">
+        <v>0</v>
+      </c>
+      <c r="F320" s="45">
+        <v>0</v>
+      </c>
+      <c r="G320" s="45">
+        <v>0</v>
+      </c>
+      <c r="H320" s="45">
         <v>30.2</v>
       </c>
-      <c r="I320" s="64">
-        <v>0</v>
-      </c>
-      <c r="J320" s="65"/>
-      <c r="K320" s="58"/>
-      <c r="L320" s="58"/>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A321" s="58" t="s">
+      <c r="I320" s="45">
+        <v>0</v>
+      </c>
+      <c r="J320" s="45"/>
+      <c r="K320" s="46"/>
+      <c r="L320" s="44"/>
+      <c r="M320" s="44"/>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A321" s="44" t="s">
         <v>358</v>
       </c>
-      <c r="B321" s="59">
+      <c r="B321" s="45">
         <v>107</v>
       </c>
-      <c r="C321" s="60">
+      <c r="C321" s="45">
         <v>1.2</v>
       </c>
-      <c r="D321" s="60">
+      <c r="D321" s="45">
         <v>0.2</v>
       </c>
-      <c r="E321" s="61">
-        <v>0</v>
-      </c>
-      <c r="F321" s="61">
-        <v>0</v>
-      </c>
-      <c r="G321" s="62">
-        <v>0</v>
-      </c>
-      <c r="H321" s="63">
+      <c r="E321" s="45">
+        <v>0</v>
+      </c>
+      <c r="F321" s="45">
+        <v>0</v>
+      </c>
+      <c r="G321" s="45">
+        <v>0</v>
+      </c>
+      <c r="H321" s="45">
         <v>24</v>
       </c>
-      <c r="I321" s="64">
+      <c r="I321" s="45">
         <v>1.2</v>
       </c>
-      <c r="J321" s="65"/>
-      <c r="K321" s="66">
+      <c r="J321" s="45"/>
+      <c r="K321" s="46">
         <v>45222</v>
       </c>
-      <c r="L321" s="58"/>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A322" s="58" t="s">
+      <c r="L321" s="44"/>
+      <c r="M321" s="44"/>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A322" s="44" t="s">
         <v>359</v>
       </c>
-      <c r="B322" s="59">
+      <c r="B322" s="45">
         <v>348</v>
       </c>
-      <c r="C322" s="60">
+      <c r="C322" s="45">
         <v>13</v>
       </c>
-      <c r="D322" s="60">
+      <c r="D322" s="45">
         <v>5</v>
       </c>
-      <c r="E322" s="61">
+      <c r="E322" s="45">
         <v>50</v>
       </c>
-      <c r="F322" s="61">
+      <c r="F322" s="45">
         <v>0.9</v>
       </c>
-      <c r="G322" s="62">
+      <c r="G322" s="45">
         <v>2.5</v>
       </c>
-      <c r="H322" s="63">
+      <c r="H322" s="45">
         <v>6.8</v>
       </c>
-      <c r="I322" s="64">
+      <c r="I322" s="45">
         <v>4.75</v>
       </c>
-      <c r="J322" s="65"/>
-      <c r="K322" s="58"/>
-      <c r="L322" s="58"/>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A323" s="58" t="s">
+      <c r="J322" s="45"/>
+      <c r="K322" s="46"/>
+      <c r="L322" s="44"/>
+      <c r="M322" s="44"/>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A323" s="44" t="s">
         <v>360</v>
       </c>
-      <c r="B323" s="59">
+      <c r="B323" s="45">
         <v>325</v>
       </c>
-      <c r="C323" s="60">
+      <c r="C323" s="45">
         <v>14.3</v>
       </c>
-      <c r="D323" s="60">
-        <v>0</v>
-      </c>
-      <c r="E323" s="61">
+      <c r="D323" s="45">
+        <v>0</v>
+      </c>
+      <c r="E323" s="45">
         <v>35.5</v>
       </c>
-      <c r="F323" s="61">
-        <v>0</v>
-      </c>
-      <c r="G323" s="62">
-        <v>0</v>
-      </c>
-      <c r="H323" s="63">
+      <c r="F323" s="45">
+        <v>0</v>
+      </c>
+      <c r="G323" s="45">
+        <v>0</v>
+      </c>
+      <c r="H323" s="45">
         <v>13.3</v>
       </c>
-      <c r="I323" s="64">
+      <c r="I323" s="45">
         <v>0.1</v>
       </c>
-      <c r="J323" s="65"/>
-      <c r="K323" s="66">
+      <c r="J323" s="45"/>
+      <c r="K323" s="46">
         <v>45206</v>
       </c>
-      <c r="L323" s="58" t="s">
+      <c r="L323" s="44" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A324" s="58" t="s">
+      <c r="M323" s="44"/>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A324" s="44" t="s">
         <v>362</v>
       </c>
-      <c r="B324" s="59">
+      <c r="B324" s="45">
         <v>242</v>
       </c>
-      <c r="C324" s="60">
+      <c r="C324" s="45">
         <v>11</v>
       </c>
-      <c r="D324" s="60">
+      <c r="D324" s="45">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E324" s="61">
+      <c r="E324" s="45">
         <v>23</v>
       </c>
-      <c r="F324" s="61">
+      <c r="F324" s="45">
         <v>1.4</v>
       </c>
-      <c r="G324" s="62">
+      <c r="G324" s="45">
         <v>1.7</v>
       </c>
-      <c r="H324" s="63">
+      <c r="H324" s="45">
         <v>12</v>
       </c>
-      <c r="I324" s="64">
+      <c r="I324" s="45">
         <v>1.4</v>
       </c>
-      <c r="J324" s="65"/>
-      <c r="K324" s="66">
+      <c r="J324" s="45"/>
+      <c r="K324" s="46">
         <v>45223</v>
       </c>
-      <c r="L324" s="58"/>
-    </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A325" s="58" t="s">
+      <c r="L324" s="44"/>
+      <c r="M324" s="44"/>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A325" s="44" t="s">
         <v>363</v>
       </c>
-      <c r="B325" s="59">
+      <c r="B325" s="45">
         <v>80</v>
       </c>
-      <c r="C325" s="60">
+      <c r="C325" s="45">
         <v>0.31</v>
       </c>
-      <c r="D325" s="60">
+      <c r="D325" s="45">
         <v>0.04</v>
       </c>
-      <c r="E325" s="61">
+      <c r="E325" s="45">
         <v>17.73</v>
       </c>
-      <c r="F325" s="61">
+      <c r="F325" s="45">
         <v>0.2</v>
       </c>
-      <c r="G325" s="62">
+      <c r="G325" s="45">
         <v>0.49</v>
       </c>
-      <c r="H325" s="63">
+      <c r="H325" s="45">
         <v>1.97</v>
       </c>
-      <c r="I325" s="64">
+      <c r="I325" s="45">
         <v>0.75</v>
       </c>
-      <c r="J325" s="65"/>
-      <c r="K325" s="66">
+      <c r="J325" s="45"/>
+      <c r="K325" s="46">
         <v>45183</v>
       </c>
-      <c r="L325" s="58" t="s">
+      <c r="L325" s="44" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A326" s="58" t="s">
+      <c r="M325" s="44"/>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A326" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="B326" s="59">
+      <c r="B326" s="45">
         <v>182</v>
       </c>
-      <c r="C326" s="60">
+      <c r="C326" s="45">
         <v>12</v>
       </c>
-      <c r="D326" s="60"/>
-      <c r="E326" s="61">
+      <c r="D326" s="45"/>
+      <c r="E326" s="45">
         <v>0.9</v>
       </c>
-      <c r="F326" s="61">
+      <c r="F326" s="45">
         <v>0.9</v>
       </c>
-      <c r="G326" s="62">
+      <c r="G326" s="45">
         <v>2.6</v>
       </c>
-      <c r="H326" s="63">
+      <c r="H326" s="45">
         <v>19.8</v>
       </c>
-      <c r="I326" s="64">
+      <c r="I326" s="45">
         <v>0.6</v>
       </c>
-      <c r="J326" s="65"/>
-      <c r="K326" s="58"/>
-      <c r="L326" s="58"/>
-    </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A327" s="58" t="s">
+      <c r="J326" s="45"/>
+      <c r="K326" s="46"/>
+      <c r="L326" s="44"/>
+      <c r="M326" s="44"/>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A327" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B327" s="59">
+      <c r="B327" s="45">
         <v>235</v>
       </c>
-      <c r="C327" s="60">
+      <c r="C327" s="45">
         <v>13.7</v>
       </c>
-      <c r="D327" s="60">
+      <c r="D327" s="45">
         <v>4.8</v>
       </c>
-      <c r="E327" s="61">
+      <c r="E327" s="45">
         <v>0.1</v>
       </c>
-      <c r="F327" s="61">
-        <v>0</v>
-      </c>
-      <c r="G327" s="62">
-        <v>0</v>
-      </c>
-      <c r="H327" s="63">
+      <c r="F327" s="45">
+        <v>0</v>
+      </c>
+      <c r="G327" s="45">
+        <v>0</v>
+      </c>
+      <c r="H327" s="45">
         <v>27.8</v>
       </c>
-      <c r="I327" s="64">
+      <c r="I327" s="45">
         <v>2.4</v>
       </c>
-      <c r="J327" s="65"/>
-      <c r="K327" s="66">
+      <c r="J327" s="45"/>
+      <c r="K327" s="46">
         <v>45181</v>
       </c>
-      <c r="L327" s="58"/>
-    </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A328" s="58" t="s">
+      <c r="L327" s="44"/>
+      <c r="M327" s="44"/>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A328" s="44" t="s">
         <v>365</v>
       </c>
-      <c r="B328" s="59"/>
-      <c r="C328" s="60"/>
-      <c r="D328" s="60"/>
-      <c r="E328" s="61"/>
-      <c r="F328" s="61"/>
-      <c r="G328" s="62"/>
-      <c r="H328" s="63"/>
-      <c r="I328" s="64"/>
-      <c r="J328" s="65"/>
-      <c r="K328" s="58"/>
-      <c r="L328" s="58"/>
-    </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A329" s="58" t="s">
+      <c r="B328" s="45"/>
+      <c r="C328" s="45"/>
+      <c r="D328" s="45"/>
+      <c r="E328" s="45"/>
+      <c r="F328" s="45"/>
+      <c r="G328" s="45"/>
+      <c r="H328" s="45"/>
+      <c r="I328" s="45"/>
+      <c r="J328" s="45"/>
+      <c r="K328" s="46"/>
+      <c r="L328" s="44"/>
+      <c r="M328" s="44"/>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A329" s="44" t="s">
         <v>366</v>
       </c>
-      <c r="B329" s="59">
+      <c r="B329" s="45">
         <v>69</v>
       </c>
-      <c r="C329" s="60">
+      <c r="C329" s="45">
         <v>1</v>
       </c>
-      <c r="D329" s="60">
+      <c r="D329" s="45">
         <v>0.6</v>
       </c>
-      <c r="E329" s="61">
+      <c r="E329" s="45">
         <v>11</v>
       </c>
-      <c r="F329" s="61">
+      <c r="F329" s="45">
         <v>3.5</v>
       </c>
-      <c r="G329" s="62">
+      <c r="G329" s="45">
         <v>7.7</v>
       </c>
-      <c r="H329" s="63">
+      <c r="H329" s="45">
         <v>3</v>
       </c>
-      <c r="I329" s="64">
+      <c r="I329" s="45">
         <v>0.06</v>
       </c>
-      <c r="J329" s="65"/>
-      <c r="K329" s="58"/>
-      <c r="L329" s="58"/>
-    </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A330" s="58" t="s">
+      <c r="J329" s="45"/>
+      <c r="K329" s="46"/>
+      <c r="L329" s="44"/>
+      <c r="M329" s="44"/>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A330" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="B330" s="59">
+      <c r="B330" s="45">
         <v>196</v>
       </c>
-      <c r="C330" s="60">
+      <c r="C330" s="45">
         <v>15.4</v>
       </c>
-      <c r="D330" s="60">
-        <v>0</v>
-      </c>
-      <c r="E330" s="61">
+      <c r="D330" s="45">
+        <v>0</v>
+      </c>
+      <c r="E330" s="45">
         <v>1.9</v>
       </c>
-      <c r="F330" s="61">
+      <c r="F330" s="45">
         <v>1.9</v>
       </c>
-      <c r="G330" s="62">
+      <c r="G330" s="45">
         <v>0.9</v>
       </c>
-      <c r="H330" s="63">
+      <c r="H330" s="45">
         <v>12</v>
       </c>
-      <c r="I330" s="64">
+      <c r="I330" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J330" s="65"/>
-      <c r="K330" s="66">
+      <c r="J330" s="45"/>
+      <c r="K330" s="46">
         <v>45190</v>
       </c>
-      <c r="L330" s="58"/>
-    </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A331" s="58" t="s">
+      <c r="L330" s="44"/>
+      <c r="M330" s="44"/>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A331" s="44" t="s">
         <v>368</v>
       </c>
-      <c r="B331" s="59">
+      <c r="B331" s="45">
         <v>493</v>
       </c>
-      <c r="C331" s="60">
+      <c r="C331" s="45">
         <v>22</v>
       </c>
-      <c r="D331" s="60">
+      <c r="D331" s="45">
         <v>4</v>
       </c>
-      <c r="E331" s="61">
+      <c r="E331" s="45">
         <v>66</v>
       </c>
-      <c r="F331" s="61">
+      <c r="F331" s="45">
         <v>28</v>
       </c>
-      <c r="G331" s="62">
+      <c r="G331" s="45">
         <v>3.5</v>
       </c>
-      <c r="H331" s="63">
+      <c r="H331" s="45">
         <v>6</v>
       </c>
-      <c r="I331" s="64">
+      <c r="I331" s="45">
         <v>0.45</v>
       </c>
-      <c r="J331" s="65"/>
-      <c r="K331" s="66">
+      <c r="J331" s="45"/>
+      <c r="K331" s="46">
         <v>45700</v>
       </c>
-      <c r="L331" s="58" t="s">
+      <c r="L331" s="44" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A332" s="58" t="s">
+      <c r="M331" s="44"/>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A332" s="44" t="s">
         <v>370</v>
       </c>
-      <c r="B332" s="59">
+      <c r="B332" s="45">
         <v>350</v>
       </c>
-      <c r="C332" s="60">
+      <c r="C332" s="45">
         <v>0.6</v>
       </c>
-      <c r="D332" s="60">
+      <c r="D332" s="45">
         <v>0.1</v>
       </c>
-      <c r="E332" s="61">
+      <c r="E332" s="45">
         <v>78</v>
       </c>
-      <c r="F332" s="61">
+      <c r="F332" s="45">
         <v>0.3</v>
       </c>
-      <c r="G332" s="62">
+      <c r="G332" s="45">
         <v>1.4</v>
       </c>
-      <c r="H332" s="63">
+      <c r="H332" s="45">
         <v>7.4</v>
       </c>
-      <c r="I332" s="64">
+      <c r="I332" s="45">
         <v>0.01</v>
       </c>
-      <c r="J332" s="65"/>
-      <c r="K332" s="66">
+      <c r="J332" s="45"/>
+      <c r="K332" s="46">
         <v>45216</v>
       </c>
-      <c r="L332" s="58"/>
-    </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A333" s="58" t="s">
+      <c r="L332" s="44"/>
+      <c r="M332" s="44"/>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A333" s="44" t="s">
         <v>371</v>
       </c>
-      <c r="B333" s="59">
+      <c r="B333" s="45">
         <v>137</v>
       </c>
-      <c r="C333" s="60">
+      <c r="C333" s="45">
         <v>2.8</v>
       </c>
-      <c r="D333" s="60"/>
-      <c r="E333" s="61">
+      <c r="D333" s="45"/>
+      <c r="E333" s="45">
         <v>25.2</v>
       </c>
-      <c r="F333" s="61">
+      <c r="F333" s="45">
         <v>0.2</v>
       </c>
-      <c r="G333" s="62">
+      <c r="G333" s="45">
         <v>0.9</v>
       </c>
-      <c r="H333" s="63">
+      <c r="H333" s="45">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I333" s="64">
+      <c r="I333" s="45">
         <v>3.3E-3</v>
       </c>
-      <c r="J333" s="65"/>
-      <c r="K333" s="66">
+      <c r="J333" s="45"/>
+      <c r="K333" s="46">
         <v>45183</v>
       </c>
-      <c r="L333" s="58"/>
-    </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A334" s="58" t="s">
+      <c r="L333" s="44"/>
+      <c r="M333" s="44"/>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A334" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="B334" s="59">
+      <c r="B334" s="45">
         <v>381</v>
       </c>
-      <c r="C334" s="60">
+      <c r="C334" s="45">
         <v>3</v>
       </c>
-      <c r="D334" s="60">
+      <c r="D334" s="45">
         <v>1</v>
       </c>
-      <c r="E334" s="61">
+      <c r="E334" s="45">
         <v>80</v>
       </c>
-      <c r="F334" s="61">
+      <c r="F334" s="45">
         <v>20</v>
       </c>
-      <c r="G334" s="62">
+      <c r="G334" s="45">
         <v>3</v>
       </c>
-      <c r="H334" s="63">
+      <c r="H334" s="45">
         <v>7</v>
       </c>
-      <c r="I334" s="64">
+      <c r="I334" s="45">
         <v>0.5</v>
       </c>
-      <c r="J334" s="65"/>
-      <c r="K334" s="66">
+      <c r="J334" s="45"/>
+      <c r="K334" s="46">
         <v>45539</v>
       </c>
-      <c r="L334" s="58"/>
-    </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A335" s="58" t="s">
+      <c r="L334" s="44"/>
+      <c r="M334" s="44"/>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A335" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="B335" s="59">
+      <c r="B335" s="45">
         <v>139</v>
       </c>
-      <c r="C335" s="60">
+      <c r="C335" s="45">
         <v>6.3</v>
       </c>
-      <c r="D335" s="60">
+      <c r="D335" s="45">
         <v>2.37</v>
       </c>
-      <c r="E335" s="61">
-        <v>0</v>
-      </c>
-      <c r="F335" s="61">
-        <v>0</v>
-      </c>
-      <c r="G335" s="62">
-        <v>0</v>
-      </c>
-      <c r="H335" s="63">
+      <c r="E335" s="45">
+        <v>0</v>
+      </c>
+      <c r="F335" s="45">
+        <v>0</v>
+      </c>
+      <c r="G335" s="45">
+        <v>0</v>
+      </c>
+      <c r="H335" s="45">
         <v>19.25</v>
       </c>
-      <c r="I335" s="64">
+      <c r="I335" s="45">
         <v>0.19</v>
       </c>
-      <c r="J335" s="65"/>
-      <c r="K335" s="66">
+      <c r="J335" s="45"/>
+      <c r="K335" s="46">
         <v>45189</v>
       </c>
-      <c r="L335" s="58"/>
-    </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A336" s="58" t="s">
+      <c r="L335" s="44"/>
+      <c r="M335" s="44"/>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A336" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="B336" s="59"/>
-      <c r="C336" s="60"/>
-      <c r="D336" s="60"/>
-      <c r="E336" s="61"/>
-      <c r="F336" s="61"/>
-      <c r="G336" s="62"/>
-      <c r="H336" s="63"/>
-      <c r="I336" s="64"/>
-      <c r="J336" s="65"/>
-      <c r="K336" s="58"/>
-      <c r="L336" s="58"/>
-    </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A337" s="58" t="s">
+      <c r="B336" s="45"/>
+      <c r="C336" s="45"/>
+      <c r="D336" s="45"/>
+      <c r="E336" s="45"/>
+      <c r="F336" s="45"/>
+      <c r="G336" s="45"/>
+      <c r="H336" s="45"/>
+      <c r="I336" s="45"/>
+      <c r="J336" s="45"/>
+      <c r="K336" s="46"/>
+      <c r="L336" s="44"/>
+      <c r="M336" s="44"/>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A337" s="44" t="s">
         <v>374</v>
       </c>
-      <c r="B337" s="59">
+      <c r="B337" s="45">
         <v>117</v>
       </c>
-      <c r="C337" s="60">
+      <c r="C337" s="45">
         <v>4.32</v>
       </c>
-      <c r="D337" s="60">
+      <c r="D337" s="45">
         <v>1</v>
       </c>
-      <c r="E337" s="61">
-        <v>0</v>
-      </c>
-      <c r="F337" s="61">
-        <v>0</v>
-      </c>
-      <c r="G337" s="62">
-        <v>0</v>
-      </c>
-      <c r="H337" s="63">
+      <c r="E337" s="45">
+        <v>0</v>
+      </c>
+      <c r="F337" s="45">
+        <v>0</v>
+      </c>
+      <c r="G337" s="45">
+        <v>0</v>
+      </c>
+      <c r="H337" s="45">
         <v>18.28</v>
       </c>
-      <c r="I337" s="64"/>
-      <c r="J337" s="65"/>
-      <c r="K337" s="66">
+      <c r="I337" s="45"/>
+      <c r="J337" s="45"/>
+      <c r="K337" s="46">
         <v>45187</v>
       </c>
-      <c r="L337" s="58"/>
-    </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A338" s="58" t="s">
+      <c r="L337" s="44"/>
+      <c r="M337" s="44"/>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A338" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="B338" s="59">
+      <c r="B338" s="45">
         <v>324</v>
       </c>
-      <c r="C338" s="60">
+      <c r="C338" s="45">
         <v>26</v>
       </c>
-      <c r="D338" s="60">
-        <v>0</v>
-      </c>
-      <c r="E338" s="61">
-        <v>0</v>
-      </c>
-      <c r="F338" s="61">
-        <v>0</v>
-      </c>
-      <c r="G338" s="62">
-        <v>0</v>
-      </c>
-      <c r="H338" s="63">
+      <c r="D338" s="45">
+        <v>0</v>
+      </c>
+      <c r="E338" s="45">
+        <v>0</v>
+      </c>
+      <c r="F338" s="45">
+        <v>0</v>
+      </c>
+      <c r="G338" s="45">
+        <v>0</v>
+      </c>
+      <c r="H338" s="45">
         <v>22</v>
       </c>
-      <c r="I338" s="64"/>
-      <c r="J338" s="65"/>
-      <c r="K338" s="58"/>
-      <c r="L338" s="58"/>
-    </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A339" s="58" t="s">
+      <c r="I338" s="45"/>
+      <c r="J338" s="45"/>
+      <c r="K338" s="46"/>
+      <c r="L338" s="44"/>
+      <c r="M338" s="44"/>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A339" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="B339" s="59">
+      <c r="B339" s="45">
         <v>369</v>
       </c>
-      <c r="C339" s="60">
+      <c r="C339" s="45">
         <v>23.5</v>
       </c>
-      <c r="D339" s="60">
+      <c r="D339" s="45">
         <v>4.8</v>
       </c>
-      <c r="E339" s="61">
+      <c r="E339" s="45">
         <v>31.3</v>
       </c>
-      <c r="F339" s="61">
+      <c r="F339" s="45">
         <v>2.4</v>
       </c>
-      <c r="G339" s="62">
+      <c r="G339" s="45">
         <v>3.4</v>
       </c>
-      <c r="H339" s="63">
+      <c r="H339" s="45">
         <v>4.3</v>
       </c>
-      <c r="I339" s="64">
+      <c r="I339" s="45">
         <v>0.8</v>
       </c>
-      <c r="J339" s="65"/>
-      <c r="K339" s="66">
+      <c r="J339" s="45"/>
+      <c r="K339" s="46">
         <v>45539</v>
       </c>
-      <c r="L339" s="58"/>
-    </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A340" s="58" t="s">
+      <c r="L339" s="44"/>
+      <c r="M339" s="44"/>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A340" s="44" t="s">
         <v>377</v>
       </c>
-      <c r="B340" s="59">
+      <c r="B340" s="45">
         <v>163</v>
       </c>
-      <c r="C340" s="60">
+      <c r="C340" s="45">
         <v>9.6</v>
       </c>
-      <c r="D340" s="60">
+      <c r="D340" s="45">
         <v>2</v>
       </c>
-      <c r="E340" s="61">
+      <c r="E340" s="45">
         <v>7.9</v>
       </c>
-      <c r="F340" s="61">
+      <c r="F340" s="45">
         <v>1.3</v>
       </c>
-      <c r="G340" s="62">
-        <v>0</v>
-      </c>
-      <c r="H340" s="63">
+      <c r="G340" s="45">
+        <v>0</v>
+      </c>
+      <c r="H340" s="45">
         <v>9.9</v>
       </c>
-      <c r="I340" s="64">
+      <c r="I340" s="45">
         <v>0.1</v>
       </c>
-      <c r="J340" s="65"/>
-      <c r="K340" s="66">
+      <c r="J340" s="45"/>
+      <c r="K340" s="46">
         <v>45215</v>
       </c>
-      <c r="L340" s="58"/>
-    </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A341" s="58" t="s">
+      <c r="L340" s="44"/>
+      <c r="M340" s="44"/>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A341" s="44" t="s">
         <v>378</v>
       </c>
-      <c r="B341" s="59">
+      <c r="B341" s="45">
         <v>348</v>
       </c>
-      <c r="C341" s="60">
+      <c r="C341" s="45">
         <v>20</v>
       </c>
-      <c r="D341" s="60">
+      <c r="D341" s="45">
         <v>4.1059999999999999</v>
       </c>
-      <c r="E341" s="61">
+      <c r="E341" s="45">
         <v>34</v>
       </c>
-      <c r="F341" s="61">
+      <c r="F341" s="45">
         <v>0.7</v>
       </c>
-      <c r="G341" s="62">
+      <c r="G341" s="45">
         <v>1.5</v>
       </c>
-      <c r="H341" s="63">
+      <c r="H341" s="45">
         <v>7.6</v>
       </c>
-      <c r="I341" s="64">
+      <c r="I341" s="45">
         <v>0.86</v>
       </c>
-      <c r="J341" s="65"/>
-      <c r="K341" s="66">
+      <c r="J341" s="45"/>
+      <c r="K341" s="46">
         <v>45219</v>
       </c>
-      <c r="L341" s="58"/>
-    </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A342" s="58" t="s">
+      <c r="L341" s="44"/>
+      <c r="M341" s="44"/>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A342" s="44" t="s">
         <v>379</v>
       </c>
-      <c r="B342" s="59">
+      <c r="B342" s="45">
         <v>255</v>
       </c>
-      <c r="C342" s="60">
+      <c r="C342" s="45">
         <v>18.7</v>
       </c>
-      <c r="D342" s="60">
+      <c r="D342" s="45">
         <v>12.5</v>
       </c>
-      <c r="E342" s="61">
+      <c r="E342" s="45">
         <v>3</v>
       </c>
-      <c r="F342" s="61">
+      <c r="F342" s="45">
         <v>3</v>
       </c>
-      <c r="G342" s="62">
-        <v>0</v>
-      </c>
-      <c r="H342" s="63">
+      <c r="G342" s="45">
+        <v>0</v>
+      </c>
+      <c r="H342" s="45">
         <v>17</v>
       </c>
-      <c r="I342" s="64"/>
-      <c r="J342" s="65"/>
-      <c r="K342" s="66">
+      <c r="I342" s="45"/>
+      <c r="J342" s="45"/>
+      <c r="K342" s="46">
         <v>45510</v>
       </c>
-      <c r="L342" s="58" t="s">
+      <c r="L342" s="44" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A343" s="58" t="s">
+      <c r="M342" s="44"/>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A343" s="44" t="s">
         <v>381</v>
       </c>
-      <c r="B343" s="59">
+      <c r="B343" s="45">
         <f>357</f>
         <v>357</v>
       </c>
-      <c r="C343" s="60">
+      <c r="C343" s="45">
         <f>1.5</f>
         <v>1.5</v>
       </c>
-      <c r="D343" s="60">
+      <c r="D343" s="45">
         <f>0.3</f>
         <v>0.3</v>
       </c>
-      <c r="E343" s="61">
+      <c r="E343" s="45">
         <f>69</f>
         <v>69</v>
       </c>
-      <c r="F343" s="61">
+      <c r="F343" s="45">
         <f>1.4</f>
         <v>1.4</v>
       </c>
-      <c r="G343" s="62">
+      <c r="G343" s="45">
         <f>3.5</f>
         <v>3.5</v>
       </c>
-      <c r="H343" s="63">
+      <c r="H343" s="45">
         <f>15</f>
         <v>15</v>
       </c>
-      <c r="I343" s="64">
+      <c r="I343" s="45">
         <v>0.46</v>
       </c>
-      <c r="J343" s="65"/>
-      <c r="K343" s="66">
+      <c r="J343" s="45"/>
+      <c r="K343" s="46">
         <v>45189</v>
       </c>
-      <c r="L343" s="58"/>
-    </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A344" s="58" t="s">
+      <c r="L343" s="44"/>
+      <c r="M343" s="44"/>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A344" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="B344" s="59">
+      <c r="B344" s="45">
         <v>297</v>
       </c>
-      <c r="C344" s="60">
+      <c r="C344" s="45">
         <v>19</v>
       </c>
-      <c r="D344" s="60">
+      <c r="D344" s="45">
         <v>6.6</v>
       </c>
-      <c r="E344" s="61">
+      <c r="E344" s="45">
         <v>0.5</v>
       </c>
-      <c r="F344" s="61">
+      <c r="F344" s="45">
         <v>0.5</v>
       </c>
-      <c r="G344" s="62">
-        <v>0</v>
-      </c>
-      <c r="H344" s="63">
+      <c r="G344" s="45">
+        <v>0</v>
+      </c>
+      <c r="H344" s="45">
         <v>31</v>
       </c>
-      <c r="I344" s="64">
+      <c r="I344" s="45">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J344" s="65"/>
-      <c r="K344" s="66">
+      <c r="J344" s="45"/>
+      <c r="K344" s="46">
         <v>45188</v>
       </c>
-      <c r="L344" s="58"/>
-    </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A345" s="58" t="s">
+      <c r="L344" s="44"/>
+      <c r="M344" s="44"/>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A345" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="B345" s="59">
+      <c r="B345" s="45">
         <v>314</v>
       </c>
-      <c r="C345" s="60">
+      <c r="C345" s="45">
         <v>27</v>
       </c>
-      <c r="D345" s="60">
+      <c r="D345" s="45">
         <v>19</v>
       </c>
-      <c r="E345" s="61">
+      <c r="E345" s="45">
         <v>2.6</v>
       </c>
-      <c r="F345" s="61">
+      <c r="F345" s="45">
         <v>1.6</v>
       </c>
-      <c r="G345" s="62">
-        <v>0</v>
-      </c>
-      <c r="H345" s="63">
+      <c r="G345" s="45">
+        <v>0</v>
+      </c>
+      <c r="H345" s="45">
         <v>14</v>
       </c>
-      <c r="I345" s="64">
+      <c r="I345" s="45">
         <v>0.9</v>
       </c>
-      <c r="J345" s="65"/>
-      <c r="K345" s="66">
+      <c r="J345" s="45"/>
+      <c r="K345" s="46">
         <v>45537</v>
       </c>
-      <c r="L345" s="58"/>
-    </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A346" s="58" t="s">
+      <c r="L345" s="44"/>
+      <c r="M345" s="44"/>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A346" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="B346" s="59">
+      <c r="B346" s="45">
         <v>248</v>
       </c>
-      <c r="C346" s="60">
+      <c r="C346" s="45">
         <v>20</v>
       </c>
-      <c r="D346" s="60">
+      <c r="D346" s="45">
         <v>6.9</v>
       </c>
-      <c r="E346" s="61">
+      <c r="E346" s="45">
         <v>3.7</v>
       </c>
-      <c r="F346" s="61">
+      <c r="F346" s="45">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G346" s="62">
+      <c r="G346" s="45">
         <v>1.3</v>
       </c>
-      <c r="H346" s="63">
+      <c r="H346" s="45">
         <v>2.4</v>
       </c>
-      <c r="I346" s="64">
+      <c r="I346" s="45">
         <v>1.2</v>
       </c>
-      <c r="J346" s="65"/>
-      <c r="K346" s="66">
+      <c r="J346" s="45"/>
+      <c r="K346" s="46">
         <v>45194</v>
       </c>
-      <c r="L346" s="58"/>
-    </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A347" s="58" t="s">
+      <c r="L346" s="44"/>
+      <c r="M346" s="44"/>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A347" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="B347" s="59">
+      <c r="B347" s="45">
         <v>74</v>
       </c>
-      <c r="C347" s="60">
+      <c r="C347" s="45">
         <v>3.5</v>
       </c>
-      <c r="D347" s="60">
+      <c r="D347" s="45">
         <v>0.6</v>
       </c>
-      <c r="E347" s="61">
+      <c r="E347" s="45">
         <v>7.5</v>
       </c>
-      <c r="F347" s="61">
+      <c r="F347" s="45">
         <v>6</v>
       </c>
-      <c r="G347" s="62">
+      <c r="G347" s="45">
         <v>2</v>
       </c>
-      <c r="H347" s="63">
+      <c r="H347" s="45">
         <v>1.5</v>
       </c>
-      <c r="I347" s="64">
+      <c r="I347" s="45">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="J347" s="65"/>
-      <c r="K347" s="66">
+      <c r="J347" s="45"/>
+      <c r="K347" s="46">
         <v>45182</v>
       </c>
-      <c r="L347" s="58" t="s">
+      <c r="L347" s="44" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A348" s="58" t="s">
+      <c r="M347" s="44"/>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A348" s="44" t="s">
         <v>385</v>
       </c>
-      <c r="B348" s="59">
+      <c r="B348" s="45">
         <v>470</v>
       </c>
-      <c r="C348" s="60">
+      <c r="C348" s="45">
         <v>15.7</v>
       </c>
-      <c r="D348" s="60">
+      <c r="D348" s="45">
         <v>5.2</v>
       </c>
-      <c r="E348" s="61">
+      <c r="E348" s="45">
         <v>74.400000000000006</v>
       </c>
-      <c r="F348" s="61">
+      <c r="F348" s="45">
         <v>1.9</v>
       </c>
-      <c r="G348" s="62">
+      <c r="G348" s="45">
         <v>0.6</v>
       </c>
-      <c r="H348" s="63">
+      <c r="H348" s="45">
         <v>7.5</v>
       </c>
-      <c r="I348" s="64">
+      <c r="I348" s="45">
         <v>2.5</v>
       </c>
-      <c r="J348" s="65">
+      <c r="J348" s="45">
         <v>0.54</v>
       </c>
-      <c r="K348" s="66">
+      <c r="K348" s="46">
         <v>45179</v>
       </c>
-      <c r="L348" s="58" t="s">
+      <c r="L348" s="44" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A349" s="58" t="s">
+      <c r="M348" s="44"/>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A349" s="44" t="s">
         <v>387</v>
       </c>
-      <c r="B349" s="59">
+      <c r="B349" s="45">
         <v>283</v>
       </c>
-      <c r="C349" s="60">
+      <c r="C349" s="45">
         <v>18.2</v>
       </c>
-      <c r="D349" s="60">
+      <c r="D349" s="45">
         <v>10.53</v>
       </c>
-      <c r="E349" s="61">
+      <c r="E349" s="45">
         <v>24.41</v>
       </c>
-      <c r="F349" s="61">
+      <c r="F349" s="45">
         <v>16</v>
       </c>
-      <c r="G349" s="62">
+      <c r="G349" s="45">
         <v>0.9</v>
       </c>
-      <c r="H349" s="63">
+      <c r="H349" s="45">
         <v>4.7699999999999996</v>
       </c>
-      <c r="I349" s="64">
+      <c r="I349" s="45">
         <v>0.21</v>
       </c>
-      <c r="J349" s="65"/>
-      <c r="K349" s="66">
+      <c r="J349" s="45"/>
+      <c r="K349" s="46">
         <v>45218</v>
       </c>
-      <c r="L349" s="58"/>
-    </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A350" s="58" t="s">
+      <c r="L349" s="44"/>
+      <c r="M349" s="44"/>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A350" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="B350" s="59">
+      <c r="B350" s="45">
         <v>301</v>
       </c>
-      <c r="C350" s="60">
+      <c r="C350" s="45">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D350" s="60">
+      <c r="D350" s="45">
         <v>3.6</v>
       </c>
-      <c r="E350" s="61">
+      <c r="E350" s="45">
         <v>39</v>
       </c>
-      <c r="F350" s="61">
+      <c r="F350" s="45">
         <v>3.4</v>
       </c>
-      <c r="G350" s="62">
+      <c r="G350" s="45">
         <v>2.5</v>
       </c>
-      <c r="H350" s="63">
+      <c r="H350" s="45">
         <v>13</v>
       </c>
-      <c r="I350" s="64">
+      <c r="I350" s="45">
         <v>1.5</v>
       </c>
-      <c r="J350" s="65"/>
-      <c r="K350" s="66">
+      <c r="J350" s="45"/>
+      <c r="K350" s="46">
         <v>45210</v>
       </c>
-      <c r="L350" s="58" t="s">
+      <c r="L350" s="44" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A351" s="58" t="s">
+      <c r="M350" s="44"/>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A351" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="B351" s="59">
+      <c r="B351" s="45">
         <v>461</v>
       </c>
-      <c r="C351" s="60">
+      <c r="C351" s="45">
         <v>18</v>
       </c>
-      <c r="D351" s="60">
+      <c r="D351" s="45">
         <v>1.7</v>
       </c>
-      <c r="E351" s="61">
+      <c r="E351" s="45">
         <v>65</v>
       </c>
-      <c r="F351" s="61">
+      <c r="F351" s="45">
         <v>9.1</v>
       </c>
-      <c r="G351" s="62">
+      <c r="G351" s="45">
         <v>3.5</v>
       </c>
-      <c r="H351" s="63">
+      <c r="H351" s="45">
         <v>8.3000000000000007</v>
       </c>
-      <c r="I351" s="64">
+      <c r="I351" s="45">
         <v>1.71</v>
       </c>
-      <c r="J351" s="65">
+      <c r="J351" s="45">
         <v>0.77</v>
       </c>
-      <c r="K351" s="66">
+      <c r="K351" s="46">
         <v>45179</v>
       </c>
-      <c r="L351" s="58" t="s">
+      <c r="L351" s="44" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A352" s="58" t="s">
+      <c r="M351" s="44"/>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A352" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="B352" s="59">
+      <c r="B352" s="45">
         <v>427</v>
       </c>
-      <c r="C352" s="60">
+      <c r="C352" s="45">
         <v>5</v>
       </c>
-      <c r="D352" s="60">
-        <v>0</v>
-      </c>
-      <c r="E352" s="61">
+      <c r="D352" s="45">
+        <v>0</v>
+      </c>
+      <c r="E352" s="45">
         <v>21.5</v>
       </c>
-      <c r="F352" s="61"/>
-      <c r="G352" s="62">
-        <v>0</v>
-      </c>
-      <c r="H352" s="63">
+      <c r="F352" s="45"/>
+      <c r="G352" s="45">
+        <v>0</v>
+      </c>
+      <c r="H352" s="45">
         <v>2.6</v>
       </c>
-      <c r="I352" s="64">
+      <c r="I352" s="45">
         <v>2.5</v>
       </c>
-      <c r="J352" s="65"/>
-      <c r="K352" s="66">
+      <c r="J352" s="45"/>
+      <c r="K352" s="46">
         <v>45184</v>
       </c>
-      <c r="L352" s="58"/>
-    </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A353" s="58" t="s">
+      <c r="L352" s="44"/>
+      <c r="M352" s="44"/>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A353" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="B353" s="59">
+      <c r="B353" s="45">
         <v>128</v>
       </c>
-      <c r="C353" s="60">
+      <c r="C353" s="45">
         <v>8.6999999999999993</v>
       </c>
-      <c r="D353" s="60">
+      <c r="D353" s="45">
         <v>3.17</v>
       </c>
-      <c r="E353" s="61">
-        <v>0</v>
-      </c>
-      <c r="F353" s="61">
-        <v>0</v>
-      </c>
-      <c r="G353" s="62">
-        <v>0</v>
-      </c>
-      <c r="H353" s="63">
+      <c r="E353" s="45">
+        <v>0</v>
+      </c>
+      <c r="F353" s="45">
+        <v>0</v>
+      </c>
+      <c r="G353" s="45">
+        <v>0</v>
+      </c>
+      <c r="H353" s="45">
         <v>12.4</v>
       </c>
-      <c r="I353" s="64">
-        <v>0</v>
-      </c>
-      <c r="J353" s="65"/>
-      <c r="K353" s="58"/>
-      <c r="L353" s="58" t="s">
+      <c r="I353" s="45">
+        <v>0</v>
+      </c>
+      <c r="J353" s="45"/>
+      <c r="K353" s="46"/>
+      <c r="L353" s="44" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A354" s="58" t="s">
+      <c r="M353" s="44"/>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A354" s="44" t="s">
         <v>394</v>
       </c>
-      <c r="B354" s="59">
+      <c r="B354" s="45">
         <v>107</v>
       </c>
-      <c r="C354" s="60">
+      <c r="C354" s="45">
         <v>7.5</v>
       </c>
-      <c r="D354" s="60">
+      <c r="D354" s="45">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E354" s="61">
+      <c r="E354" s="45">
         <v>0.6</v>
       </c>
-      <c r="F354" s="61">
-        <v>0</v>
-      </c>
-      <c r="G354" s="62">
-        <v>0</v>
-      </c>
-      <c r="H354" s="63">
+      <c r="F354" s="45">
+        <v>0</v>
+      </c>
+      <c r="G354" s="45">
+        <v>0</v>
+      </c>
+      <c r="H354" s="45">
         <v>9.1999999999999993</v>
       </c>
-      <c r="I354" s="64">
+      <c r="I354" s="45">
         <v>1.4</v>
       </c>
-      <c r="J354" s="65"/>
-      <c r="K354" s="66">
+      <c r="J354" s="45"/>
+      <c r="K354" s="46">
         <v>45189</v>
       </c>
-      <c r="L354" s="58"/>
-    </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A355" s="58" t="s">
+      <c r="L354" s="44"/>
+      <c r="M354" s="44"/>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A355" s="44" t="s">
         <v>395</v>
       </c>
-      <c r="B355" s="59">
+      <c r="B355" s="45">
         <v>501</v>
       </c>
-      <c r="C355" s="60">
+      <c r="C355" s="45">
         <v>25</v>
       </c>
-      <c r="D355" s="60">
+      <c r="D355" s="45">
         <v>21</v>
       </c>
-      <c r="E355" s="61">
+      <c r="E355" s="45">
         <v>58</v>
       </c>
-      <c r="F355" s="61">
+      <c r="F355" s="45">
         <v>25</v>
       </c>
-      <c r="G355" s="62">
-        <v>0</v>
-      </c>
-      <c r="H355" s="63">
+      <c r="G355" s="45">
+        <v>0</v>
+      </c>
+      <c r="H355" s="45">
         <v>8.1999999999999993</v>
       </c>
-      <c r="I355" s="64">
+      <c r="I355" s="45">
         <v>0.35</v>
       </c>
-      <c r="J355" s="65"/>
-      <c r="K355" s="66">
+      <c r="J355" s="45"/>
+      <c r="K355" s="46">
         <v>45202</v>
       </c>
-      <c r="L355" s="58"/>
-    </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A356" s="58" t="s">
+      <c r="L355" s="44"/>
+      <c r="M355" s="44"/>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A356" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="B356" s="59">
+      <c r="B356" s="45">
         <v>517</v>
       </c>
-      <c r="C356" s="60">
+      <c r="C356" s="45">
         <v>27</v>
       </c>
-      <c r="D356" s="60">
+      <c r="D356" s="45">
         <v>19</v>
       </c>
-      <c r="E356" s="61">
+      <c r="E356" s="45">
         <v>58</v>
       </c>
-      <c r="F356" s="61">
+      <c r="F356" s="45">
         <v>25</v>
       </c>
-      <c r="G356" s="62">
-        <v>0</v>
-      </c>
-      <c r="H356" s="63">
+      <c r="G356" s="45">
+        <v>0</v>
+      </c>
+      <c r="H356" s="45">
         <v>8.6</v>
       </c>
-      <c r="I356" s="64">
+      <c r="I356" s="45">
         <v>0.37</v>
       </c>
-      <c r="J356" s="65"/>
-      <c r="K356" s="66">
+      <c r="J356" s="45"/>
+      <c r="K356" s="46">
         <v>45211</v>
       </c>
-      <c r="L356" s="58" t="s">
+      <c r="L356" s="44" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A357" s="49" t="s">
+      <c r="M356" s="44"/>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A357" s="44" t="s">
         <v>398</v>
       </c>
-      <c r="B357" s="50">
+      <c r="B357" s="45">
         <v>259</v>
       </c>
-      <c r="C357" s="51">
+      <c r="C357" s="45">
         <v>22.2</v>
       </c>
-      <c r="D357" s="51">
-        <v>0</v>
-      </c>
-      <c r="E357" s="52">
+      <c r="D357" s="45">
+        <v>0</v>
+      </c>
+      <c r="E357" s="45">
         <v>0.3</v>
       </c>
-      <c r="F357" s="52">
-        <v>0</v>
-      </c>
-      <c r="G357" s="53">
-        <v>0</v>
-      </c>
-      <c r="H357" s="54">
+      <c r="F357" s="45">
+        <v>0</v>
+      </c>
+      <c r="G357" s="45">
+        <v>0</v>
+      </c>
+      <c r="H357" s="45">
         <v>14.6</v>
       </c>
-      <c r="I357" s="55">
-        <v>0</v>
-      </c>
-      <c r="J357" s="56"/>
-      <c r="K357" s="57">
+      <c r="I357" s="45">
+        <v>0</v>
+      </c>
+      <c r="J357" s="45"/>
+      <c r="K357" s="46">
         <v>45201</v>
       </c>
-      <c r="L357" s="49" t="s">
+      <c r="L357" s="44" t="s">
         <v>399</v>
       </c>
+      <c r="M357" s="44"/>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A358" s="44"/>
+      <c r="B358" s="45"/>
+      <c r="C358" s="45"/>
+      <c r="D358" s="45"/>
+      <c r="E358" s="45"/>
+      <c r="F358" s="45"/>
+      <c r="G358" s="45"/>
+      <c r="H358" s="45"/>
+      <c r="I358" s="45"/>
+      <c r="J358" s="45"/>
+      <c r="K358" s="46"/>
+      <c r="L358" s="44"/>
+      <c r="M358" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M270" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e36746ea3f026f8f/Documenti/GitHub/Dilah96.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4E4B81-441F-41A7-8872-253D72B81C3E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8058225-7ECF-4744-8807-6A693E1C768C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alimenti" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="397">
   <si>
     <t>Cibo</t>
   </si>
@@ -944,9 +944,6 @@
     <t>Asiago</t>
   </si>
   <si>
-    <t>Baccala vicentina</t>
-  </si>
-  <si>
     <t>Bacon</t>
   </si>
   <si>
@@ -1136,9 +1133,6 @@
     <t>50g a fetta</t>
   </si>
   <si>
-    <t>Prosciutto crudo 36 mesi</t>
-  </si>
-  <si>
     <t>Purè</t>
   </si>
   <si>
@@ -1164,9 +1158,6 @@
   </si>
   <si>
     <t xml:space="preserve">Salmone </t>
-  </si>
-  <si>
-    <t>Salsiccia</t>
   </si>
   <si>
     <t>Samosa</t>
@@ -1748,21 +1739,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M358"/>
+  <dimension ref="A1:M354"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11256,7 +11248,9 @@
       <c r="L271" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="M271" s="44"/>
+      <c r="M271" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="44" t="s">
@@ -11291,7 +11285,9 @@
         <v>45183</v>
       </c>
       <c r="L272" s="44"/>
-      <c r="M272" s="44"/>
+      <c r="M272" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="44" t="s">
@@ -11324,7 +11320,9 @@
       <c r="J273" s="45"/>
       <c r="K273" s="46"/>
       <c r="L273" s="44"/>
-      <c r="M273" s="44"/>
+      <c r="M273" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="44" t="s">
@@ -11359,1240 +11357,1332 @@
         <v>45187</v>
       </c>
       <c r="L274" s="44"/>
-      <c r="M274" s="44"/>
+      <c r="M274" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="B275" s="45"/>
-      <c r="C275" s="45"/>
-      <c r="D275" s="45"/>
-      <c r="E275" s="45"/>
-      <c r="F275" s="45"/>
-      <c r="G275" s="45"/>
-      <c r="H275" s="45"/>
-      <c r="I275" s="45"/>
+      <c r="B275" s="45">
+        <v>393</v>
+      </c>
+      <c r="C275" s="45">
+        <v>37.1</v>
+      </c>
+      <c r="D275" s="45">
+        <v>12.6</v>
+      </c>
+      <c r="E275" s="45">
+        <v>0</v>
+      </c>
+      <c r="F275" s="45">
+        <v>0</v>
+      </c>
+      <c r="G275" s="45">
+        <v>0</v>
+      </c>
+      <c r="H275" s="45">
+        <v>13.7</v>
+      </c>
+      <c r="I275" s="45">
+        <v>0.75</v>
+      </c>
       <c r="J275" s="45"/>
       <c r="K275" s="46"/>
       <c r="L275" s="44"/>
-      <c r="M275" s="44"/>
+      <c r="M275" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="44" t="s">
         <v>302</v>
       </c>
       <c r="B276" s="45">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="C276" s="45">
-        <v>37.1</v>
+        <v>16</v>
       </c>
       <c r="D276" s="45">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="E276" s="45">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F276" s="45">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G276" s="45">
         <v>0</v>
       </c>
       <c r="H276" s="45">
-        <v>13.7</v>
+        <v>32</v>
       </c>
       <c r="I276" s="45">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="J276" s="45"/>
       <c r="K276" s="46"/>
-      <c r="L276" s="44"/>
-      <c r="M276" s="44"/>
+      <c r="L276" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="M276" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B277" s="45">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="C277" s="45">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D277" s="45">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="E277" s="45">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F277" s="45">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G277" s="45">
         <v>0</v>
       </c>
       <c r="H277" s="45">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I277" s="45">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="J277" s="45"/>
-      <c r="K277" s="46"/>
+      <c r="K277" s="46">
+        <v>45194</v>
+      </c>
       <c r="L277" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="M277" s="44"/>
+        <v>305</v>
+      </c>
+      <c r="M277" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B278" s="45">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C278" s="45">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D278" s="45">
-        <v>5.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E278" s="45">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="F278" s="45">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G278" s="45">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H278" s="45">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I278" s="45">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="J278" s="45"/>
       <c r="K278" s="46">
-        <v>45194</v>
+        <v>45188</v>
       </c>
       <c r="L278" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="M278" s="44"/>
+        <v>307</v>
+      </c>
+      <c r="M278" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B279" s="45">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="C279" s="45">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="D279" s="45">
-        <v>4.0999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="E279" s="45">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F279" s="45">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G279" s="45">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H279" s="45">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I279" s="45">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="J279" s="45"/>
-      <c r="K279" s="46">
-        <v>45188</v>
-      </c>
+      <c r="K279" s="46"/>
       <c r="L279" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="M279" s="44"/>
+        <v>309</v>
+      </c>
+      <c r="M279" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="44" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B280" s="45">
-        <v>344</v>
+        <v>187</v>
       </c>
       <c r="C280" s="45">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="D280" s="45">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E280" s="45">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F280" s="45">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G280" s="45">
         <v>0</v>
       </c>
       <c r="H280" s="45">
-        <v>19</v>
+        <v>25.4</v>
       </c>
       <c r="I280" s="45">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J280" s="45"/>
-      <c r="K280" s="46"/>
+      <c r="K280" s="46">
+        <v>45201</v>
+      </c>
       <c r="L280" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="M280" s="44"/>
+        <v>311</v>
+      </c>
+      <c r="M280" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="44" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="B281" s="45">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="C281" s="45">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="D281" s="45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E281" s="45">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F281" s="45">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G281" s="45">
         <v>0</v>
       </c>
       <c r="H281" s="45">
-        <v>25.4</v>
+        <v>32</v>
       </c>
       <c r="I281" s="45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J281" s="45"/>
-      <c r="K281" s="46">
-        <v>45201</v>
-      </c>
+      <c r="K281" s="46"/>
       <c r="L281" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="M281" s="44"/>
+      <c r="M281" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="44" t="s">
-        <v>152</v>
+        <v>313</v>
       </c>
       <c r="B282" s="45">
-        <v>151</v>
+        <v>639</v>
       </c>
       <c r="C282" s="45">
-        <v>3.6</v>
+        <v>53</v>
       </c>
       <c r="D282" s="45">
-        <v>1.7</v>
+        <v>9.5</v>
       </c>
       <c r="E282" s="45">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="F282" s="45">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="G282" s="45">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H282" s="45">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I282" s="45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J282" s="45"/>
       <c r="K282" s="46"/>
-      <c r="L282" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="M282" s="44"/>
+      <c r="L282" s="44"/>
+      <c r="M282" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="44" t="s">
         <v>314</v>
       </c>
       <c r="B283" s="45">
-        <v>639</v>
+        <v>130</v>
       </c>
       <c r="C283" s="45">
-        <v>53</v>
+        <v>1.3</v>
       </c>
       <c r="D283" s="45">
-        <v>9.5</v>
+        <v>0.6</v>
       </c>
       <c r="E283" s="45">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="F283" s="45">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="G283" s="45">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H283" s="45">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I283" s="45">
-        <v>0</v>
-      </c>
-      <c r="J283" s="45"/>
-      <c r="K283" s="46"/>
+        <v>0.65</v>
+      </c>
+      <c r="J283" s="45">
+        <v>0.95</v>
+      </c>
+      <c r="K283" s="46">
+        <v>45176</v>
+      </c>
       <c r="L283" s="44"/>
-      <c r="M283" s="44"/>
+      <c r="M283" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="44" t="s">
         <v>315</v>
       </c>
       <c r="B284" s="45">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C284" s="45">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="D284" s="45">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E284" s="45">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="F284" s="45">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="G284" s="45">
         <v>0</v>
       </c>
       <c r="H284" s="45">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="I284" s="45">
-        <v>0.65</v>
-      </c>
-      <c r="J284" s="45">
-        <v>0.95</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="J284" s="45"/>
       <c r="K284" s="46">
-        <v>45176</v>
+        <v>45180</v>
       </c>
       <c r="L284" s="44"/>
-      <c r="M284" s="44"/>
+      <c r="M284" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="44" t="s">
         <v>316</v>
       </c>
       <c r="B285" s="45">
-        <v>119</v>
+        <v>626</v>
       </c>
       <c r="C285" s="45">
-        <v>2.6</v>
+        <v>54</v>
       </c>
       <c r="D285" s="45">
-        <v>0.9</v>
+        <v>36</v>
       </c>
       <c r="E285" s="45">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F285" s="45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G285" s="45">
         <v>0</v>
       </c>
       <c r="H285" s="45">
-        <v>22.3</v>
+        <v>11</v>
       </c>
       <c r="I285" s="45">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J285" s="45"/>
       <c r="K285" s="46">
-        <v>45180</v>
+        <v>45215</v>
       </c>
       <c r="L285" s="44"/>
-      <c r="M285" s="44"/>
+      <c r="M285" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="44" t="s">
         <v>317</v>
       </c>
       <c r="B286" s="45">
-        <v>626</v>
+        <v>386</v>
       </c>
       <c r="C286" s="45">
-        <v>54</v>
+        <v>1.9</v>
       </c>
       <c r="D286" s="45">
-        <v>36</v>
+        <v>0.9</v>
       </c>
       <c r="E286" s="45">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="F286" s="45">
-        <v>1.5</v>
+        <v>17</v>
       </c>
       <c r="G286" s="45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H286" s="45">
-        <v>11</v>
+        <v>6.3</v>
       </c>
       <c r="I286" s="45">
-        <v>0</v>
-      </c>
-      <c r="J286" s="45"/>
-      <c r="K286" s="46">
-        <v>45215</v>
-      </c>
+        <v>0.65</v>
+      </c>
+      <c r="J286" s="45">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="K286" s="46"/>
       <c r="L286" s="44"/>
-      <c r="M286" s="44"/>
+      <c r="M286" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="44" t="s">
         <v>318</v>
       </c>
       <c r="B287" s="45">
-        <v>386</v>
+        <v>245</v>
       </c>
       <c r="C287" s="45">
-        <v>1.9</v>
+        <v>15</v>
       </c>
       <c r="D287" s="45">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="E287" s="45">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="F287" s="45">
         <v>17</v>
       </c>
       <c r="G287" s="45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H287" s="45">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="I287" s="45">
-        <v>0.65</v>
-      </c>
-      <c r="J287" s="45">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="K287" s="46"/>
-      <c r="L287" s="44"/>
-      <c r="M287" s="44"/>
+        <v>0.2</v>
+      </c>
+      <c r="J287" s="45"/>
+      <c r="K287" s="46">
+        <v>45543</v>
+      </c>
+      <c r="L287" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="M287" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="44" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B288" s="45">
-        <v>245</v>
+        <v>484</v>
       </c>
       <c r="C288" s="45">
-        <v>15</v>
+        <v>22.42</v>
       </c>
       <c r="D288" s="45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E288" s="45">
-        <v>26</v>
+        <v>64.48</v>
       </c>
       <c r="F288" s="45">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G288" s="45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H288" s="45">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="I288" s="45">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J288" s="45"/>
       <c r="K288" s="46">
-        <v>45543</v>
-      </c>
-      <c r="L288" s="44" t="s">
-        <v>320</v>
-      </c>
-      <c r="M288" s="44"/>
+        <v>45184</v>
+      </c>
+      <c r="L288" s="44"/>
+      <c r="M288" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="44" t="s">
         <v>321</v>
       </c>
       <c r="B289" s="45">
-        <v>484</v>
+        <v>93</v>
       </c>
       <c r="C289" s="45">
-        <v>22.42</v>
+        <v>5</v>
       </c>
       <c r="D289" s="45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E289" s="45">
-        <v>64.48</v>
+        <v>3</v>
       </c>
       <c r="F289" s="45">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G289" s="45">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H289" s="45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I289" s="45">
-        <v>0</v>
-      </c>
-      <c r="J289" s="45"/>
+        <v>0.1</v>
+      </c>
+      <c r="J289" s="45">
+        <v>0.92700000000000005</v>
+      </c>
       <c r="K289" s="46">
-        <v>45184</v>
-      </c>
-      <c r="L289" s="44"/>
-      <c r="M289" s="44"/>
+        <v>45178</v>
+      </c>
+      <c r="L289" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="M289" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="44" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B290" s="45">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C290" s="45">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="D290" s="45">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="E290" s="45">
-        <v>3</v>
+        <v>14.2</v>
       </c>
       <c r="F290" s="45">
-        <v>3</v>
+        <v>14.2</v>
       </c>
       <c r="G290" s="45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H290" s="45">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="I290" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="J290" s="45">
-        <v>0.92700000000000005</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J290" s="45"/>
       <c r="K290" s="46">
-        <v>45178</v>
+        <v>45194</v>
       </c>
       <c r="L290" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="M290" s="44"/>
+        <v>324</v>
+      </c>
+      <c r="M290" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="44" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B291" s="45">
-        <v>63</v>
+        <v>295</v>
       </c>
       <c r="C291" s="45">
-        <v>0.2</v>
+        <v>11.4</v>
       </c>
       <c r="D291" s="45">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="E291" s="45">
-        <v>14.2</v>
+        <v>41.32</v>
       </c>
       <c r="F291" s="45">
-        <v>14.2</v>
+        <v>2.36</v>
       </c>
       <c r="G291" s="45">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H291" s="45">
-        <v>0.9</v>
+        <v>6.61</v>
       </c>
       <c r="I291" s="45">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J291" s="45"/>
       <c r="K291" s="46">
-        <v>45194</v>
-      </c>
-      <c r="L291" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="M291" s="44"/>
+        <v>45201</v>
+      </c>
+      <c r="L291" s="44"/>
+      <c r="M291" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="44" t="s">
         <v>326</v>
       </c>
       <c r="B292" s="45">
-        <v>295</v>
+        <v>377</v>
       </c>
       <c r="C292" s="45">
-        <v>11.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D292" s="45">
-        <v>1.42</v>
+        <v>0.3</v>
       </c>
       <c r="E292" s="45">
-        <v>41.32</v>
+        <v>83</v>
       </c>
       <c r="F292" s="45">
-        <v>2.36</v>
+        <v>0.1</v>
       </c>
       <c r="G292" s="45">
-        <v>2.2999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="H292" s="45">
-        <v>6.61</v>
+        <v>7.3</v>
       </c>
       <c r="I292" s="45">
-        <v>0.7</v>
-      </c>
-      <c r="J292" s="45"/>
+        <v>0.8</v>
+      </c>
+      <c r="J292" s="45">
+        <v>1.26</v>
+      </c>
       <c r="K292" s="46">
-        <v>45201</v>
-      </c>
-      <c r="L292" s="44"/>
-      <c r="M292" s="44"/>
+        <v>45179</v>
+      </c>
+      <c r="L292" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="M292" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="44" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B293" s="45">
-        <v>377</v>
+        <v>24</v>
       </c>
       <c r="C293" s="45">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D293" s="45">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E293" s="45">
-        <v>83</v>
+        <v>5.9</v>
       </c>
       <c r="F293" s="45">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="G293" s="45">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H293" s="45">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I293" s="45">
-        <v>0.8</v>
+        <v>0.13</v>
       </c>
       <c r="J293" s="45">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="K293" s="46">
         <v>45179</v>
       </c>
-      <c r="L293" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="M293" s="44"/>
+      <c r="L293" s="44"/>
+      <c r="M293" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="44" t="s">
         <v>329</v>
       </c>
       <c r="B294" s="45">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="C294" s="45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D294" s="45">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="E294" s="45">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="F294" s="45">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="G294" s="45">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H294" s="45">
-        <v>0</v>
+        <v>11.84</v>
       </c>
       <c r="I294" s="45">
-        <v>0.13</v>
-      </c>
-      <c r="J294" s="45">
-        <v>1.18</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J294" s="45"/>
       <c r="K294" s="46">
-        <v>45179</v>
+        <v>45225</v>
       </c>
       <c r="L294" s="44"/>
-      <c r="M294" s="44"/>
+      <c r="M294" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="44" t="s">
         <v>330</v>
       </c>
       <c r="B295" s="45">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C295" s="45">
-        <v>10</v>
+        <v>4.22</v>
       </c>
       <c r="D295" s="45">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="E295" s="45">
-        <v>1.6</v>
+        <v>20.29</v>
       </c>
       <c r="F295" s="45">
-        <v>0.8</v>
+        <v>1.74</v>
       </c>
       <c r="G295" s="45">
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H295" s="45">
-        <v>11.84</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="I295" s="45">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="J295" s="45"/>
       <c r="K295" s="46">
-        <v>45225</v>
+        <v>45197</v>
       </c>
       <c r="L295" s="44"/>
-      <c r="M295" s="44"/>
+      <c r="M295" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="44" t="s">
         <v>331</v>
       </c>
       <c r="B296" s="45">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="C296" s="45">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="D296" s="45">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="E296" s="45">
-        <v>20.29</v>
+        <v>6.3</v>
       </c>
       <c r="F296" s="45">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="G296" s="45">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="H296" s="45">
-        <v>9.6999999999999993</v>
+        <v>0.7</v>
       </c>
       <c r="I296" s="45">
-        <v>0.67</v>
+        <v>0.12</v>
       </c>
       <c r="J296" s="45"/>
       <c r="K296" s="46">
-        <v>45197</v>
+        <v>45543</v>
       </c>
       <c r="L296" s="44"/>
-      <c r="M296" s="44"/>
+      <c r="M296" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="44" t="s">
         <v>332</v>
       </c>
       <c r="B297" s="45">
-        <v>62</v>
+        <v>232</v>
       </c>
       <c r="C297" s="45">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="D297" s="45">
+        <v>0</v>
+      </c>
+      <c r="E297" s="45">
+        <v>0.44</v>
+      </c>
+      <c r="F297" s="45">
         <v>0.4</v>
       </c>
-      <c r="E297" s="45">
-        <v>6.3</v>
-      </c>
-      <c r="F297" s="45">
-        <v>1.2</v>
-      </c>
       <c r="G297" s="45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H297" s="45">
-        <v>0.7</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="I297" s="45">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="J297" s="45"/>
       <c r="K297" s="46">
-        <v>45543</v>
+        <v>45184</v>
       </c>
       <c r="L297" s="44"/>
-      <c r="M297" s="44"/>
+      <c r="M297" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="44" t="s">
-        <v>333</v>
+        <v>270</v>
       </c>
       <c r="B298" s="45">
-        <v>232</v>
+        <v>603</v>
       </c>
       <c r="C298" s="45">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="D298" s="45">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="E298" s="45">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="F298" s="45">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G298" s="45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H298" s="45">
-        <v>17.100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I298" s="45">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J298" s="45"/>
       <c r="K298" s="46">
-        <v>45184</v>
-      </c>
-      <c r="L298" s="44"/>
-      <c r="M298" s="44"/>
+        <v>45222</v>
+      </c>
+      <c r="L298" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="M298" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" s="44" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="B299" s="45">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="C299" s="45">
-        <v>67</v>
-      </c>
-      <c r="D299" s="45">
-        <v>8.1</v>
-      </c>
+        <v>55.3</v>
+      </c>
+      <c r="D299" s="45"/>
       <c r="E299" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="F299" s="45">
-        <v>0.5</v>
-      </c>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F299" s="45"/>
       <c r="G299" s="45">
-        <v>0.5</v>
+        <v>12.7</v>
       </c>
       <c r="H299" s="45">
-        <v>0.8</v>
-      </c>
-      <c r="I299" s="45">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I299" s="45"/>
       <c r="J299" s="45"/>
       <c r="K299" s="46">
-        <v>45222</v>
-      </c>
-      <c r="L299" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="M299" s="44"/>
+        <v>45205</v>
+      </c>
+      <c r="L299" s="44"/>
+      <c r="M299" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" s="44" t="s">
         <v>335</v>
       </c>
       <c r="B300" s="45">
-        <v>628</v>
+        <v>42</v>
       </c>
       <c r="C300" s="45">
-        <v>55.3</v>
-      </c>
-      <c r="D300" s="45"/>
+        <v>2.1</v>
+      </c>
+      <c r="D300" s="45">
+        <v>0.35</v>
+      </c>
       <c r="E300" s="45">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F300" s="45"/>
+        <v>5.2</v>
+      </c>
+      <c r="F300" s="45">
+        <v>0</v>
+      </c>
       <c r="G300" s="45">
-        <v>12.7</v>
+        <v>2.8</v>
       </c>
       <c r="H300" s="45">
-        <v>22</v>
-      </c>
-      <c r="I300" s="45"/>
+        <v>1</v>
+      </c>
+      <c r="I300" s="45">
+        <v>0</v>
+      </c>
       <c r="J300" s="45"/>
       <c r="K300" s="46">
-        <v>45205</v>
+        <v>45537</v>
       </c>
       <c r="L300" s="44"/>
-      <c r="M300" s="44"/>
+      <c r="M300" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="44" t="s">
         <v>336</v>
       </c>
       <c r="B301" s="45">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C301" s="45">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="D301" s="45">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="E301" s="45">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="F301" s="45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G301" s="45">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="H301" s="45">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="I301" s="45">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J301" s="45"/>
       <c r="K301" s="46">
-        <v>45537</v>
-      </c>
-      <c r="L301" s="44"/>
-      <c r="M301" s="44"/>
+        <v>45197</v>
+      </c>
+      <c r="L301" s="44" t="s">
+        <v>337</v>
+      </c>
+      <c r="M301" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" s="44" t="s">
-        <v>337</v>
+        <v>220</v>
       </c>
       <c r="B302" s="45">
-        <v>125</v>
+        <v>304</v>
       </c>
       <c r="C302" s="45">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="D302" s="45">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E302" s="45">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F302" s="45">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="G302" s="45">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H302" s="45">
-        <v>9.4</v>
+        <v>0.3</v>
       </c>
       <c r="I302" s="45">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J302" s="45"/>
-      <c r="K302" s="46">
-        <v>45197</v>
-      </c>
-      <c r="L302" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="M302" s="44"/>
+      <c r="K302" s="46"/>
+      <c r="L302" s="44"/>
+      <c r="M302" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="44" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="B303" s="45">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C303" s="45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D303" s="45">
         <v>0</v>
       </c>
       <c r="E303" s="45">
-        <v>82</v>
+        <v>1.5</v>
       </c>
       <c r="F303" s="45">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G303" s="45">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H303" s="45">
-        <v>0.3</v>
+        <v>15.7</v>
       </c>
       <c r="I303" s="45">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J303" s="45"/>
-      <c r="K303" s="46"/>
+      <c r="K303" s="46">
+        <v>45540</v>
+      </c>
       <c r="L303" s="44"/>
-      <c r="M303" s="44"/>
+      <c r="M303" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="44" t="s">
-        <v>154</v>
+        <v>338</v>
       </c>
       <c r="B304" s="45">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="C304" s="45">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D304" s="45">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E304" s="45">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F304" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G304" s="45">
         <v>0</v>
       </c>
       <c r="H304" s="45">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="I304" s="45">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J304" s="45"/>
-      <c r="K304" s="46">
-        <v>45540</v>
-      </c>
+      <c r="K304" s="46"/>
       <c r="L304" s="44"/>
-      <c r="M304" s="44"/>
+      <c r="M304" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" s="44" t="s">
         <v>339</v>
       </c>
       <c r="B305" s="45">
-        <v>238</v>
+        <v>462</v>
       </c>
       <c r="C305" s="45">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D305" s="45">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E305" s="45">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F305" s="45">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G305" s="45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H305" s="45">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="I305" s="45">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J305" s="45"/>
-      <c r="K305" s="46"/>
+      <c r="K305" s="46">
+        <v>45189</v>
+      </c>
       <c r="L305" s="44"/>
-      <c r="M305" s="44"/>
+      <c r="M305" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306" s="44" t="s">
         <v>340</v>
       </c>
       <c r="B306" s="45">
-        <v>462</v>
+        <v>90</v>
       </c>
       <c r="C306" s="45">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="D306" s="45">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="E306" s="45">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F306" s="45">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G306" s="45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H306" s="45">
-        <v>8.5</v>
+        <v>17.36</v>
       </c>
       <c r="I306" s="45">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J306" s="45"/>
-      <c r="K306" s="46">
-        <v>45189</v>
-      </c>
+      <c r="K306" s="46"/>
       <c r="L306" s="44"/>
-      <c r="M306" s="44"/>
+      <c r="M306" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" s="44" t="s">
         <v>341</v>
       </c>
       <c r="B307" s="45">
-        <v>90</v>
+        <v>449</v>
       </c>
       <c r="C307" s="45">
+        <v>17</v>
+      </c>
+      <c r="D307" s="45">
+        <v>2.4</v>
+      </c>
+      <c r="E307" s="45">
+        <v>62.1</v>
+      </c>
+      <c r="F307" s="45">
         <v>1.8</v>
       </c>
-      <c r="D307" s="45">
-        <v>0.6</v>
-      </c>
-      <c r="E307" s="45">
-        <v>0</v>
-      </c>
-      <c r="F307" s="45">
-        <v>0</v>
-      </c>
       <c r="G307" s="45">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="H307" s="45">
-        <v>17.36</v>
+        <v>9.9</v>
       </c>
       <c r="I307" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="J307" s="45"/>
+        <v>3</v>
+      </c>
+      <c r="J307" s="45">
+        <v>0.97199999999999998</v>
+      </c>
       <c r="K307" s="46"/>
-      <c r="L307" s="44"/>
-      <c r="M307" s="44"/>
+      <c r="L307" s="44" t="s">
+        <v>342</v>
+      </c>
+      <c r="M307" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B308" s="45">
-        <v>449</v>
+        <v>539</v>
       </c>
       <c r="C308" s="45">
-        <v>17</v>
+        <v>30.9</v>
       </c>
       <c r="D308" s="45">
-        <v>2.4</v>
+        <v>10.6</v>
       </c>
       <c r="E308" s="45">
-        <v>62.1</v>
+        <v>55.5</v>
       </c>
       <c r="F308" s="45">
-        <v>1.8</v>
+        <v>56.3</v>
       </c>
       <c r="G308" s="45">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H308" s="45">
-        <v>9.9</v>
+        <v>6.3</v>
       </c>
       <c r="I308" s="45">
-        <v>3</v>
-      </c>
-      <c r="J308" s="45">
-        <v>0.97199999999999998</v>
-      </c>
+        <v>0.107</v>
+      </c>
+      <c r="J308" s="45"/>
       <c r="K308" s="46"/>
-      <c r="L308" s="44" t="s">
-        <v>343</v>
-      </c>
-      <c r="M308" s="44"/>
+      <c r="L308" s="44"/>
+      <c r="M308" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" s="44" t="s">
         <v>344</v>
       </c>
       <c r="B309" s="45">
-        <v>539</v>
+        <v>884</v>
       </c>
       <c r="C309" s="45">
-        <v>30.9</v>
+        <v>100</v>
       </c>
       <c r="D309" s="45">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="E309" s="45">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="F309" s="45">
-        <v>56.3</v>
+        <v>0</v>
       </c>
       <c r="G309" s="45">
         <v>0</v>
       </c>
       <c r="H309" s="45">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="I309" s="45">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="J309" s="45"/>
-      <c r="K309" s="46"/>
-      <c r="L309" s="44"/>
-      <c r="M309" s="44"/>
+      <c r="K309" s="46">
+        <v>45197</v>
+      </c>
+      <c r="L309" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="M309" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" s="44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B310" s="45">
-        <v>884</v>
+        <v>268</v>
       </c>
       <c r="C310" s="45">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D310" s="45">
         <v>0</v>
       </c>
       <c r="E310" s="45">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="F310" s="45">
         <v>0</v>
@@ -12601,311 +12691,327 @@
         <v>0</v>
       </c>
       <c r="H310" s="45">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="I310" s="45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J310" s="45"/>
       <c r="K310" s="46">
-        <v>45197</v>
-      </c>
-      <c r="L310" s="44" t="s">
-        <v>346</v>
-      </c>
-      <c r="M310" s="44"/>
+        <v>45229</v>
+      </c>
+      <c r="L310" s="44"/>
+      <c r="M310" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" s="44" t="s">
         <v>347</v>
       </c>
       <c r="B311" s="45">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C311" s="45">
+        <v>3.8</v>
+      </c>
+      <c r="D311" s="45">
         <v>0.5</v>
       </c>
-      <c r="D311" s="45">
-        <v>0</v>
-      </c>
       <c r="E311" s="45">
-        <v>59.5</v>
+        <v>49.7</v>
       </c>
       <c r="F311" s="45">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G311" s="45">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="H311" s="45">
-        <v>8.1</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I311" s="45">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J311" s="45"/>
       <c r="K311" s="46">
-        <v>45229</v>
-      </c>
-      <c r="L311" s="44"/>
-      <c r="M311" s="44"/>
+        <v>45222</v>
+      </c>
+      <c r="L311" s="44" t="s">
+        <v>348</v>
+      </c>
+      <c r="M311" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" s="44" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B312" s="45">
-        <v>274</v>
+        <v>371</v>
       </c>
       <c r="C312" s="45">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="D312" s="45">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E312" s="45">
-        <v>49.7</v>
+        <v>74.67</v>
       </c>
       <c r="F312" s="45">
-        <v>2.2999999999999998</v>
+        <v>2.67</v>
       </c>
       <c r="G312" s="45">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="H312" s="45">
-        <v>8.8000000000000007</v>
+        <v>13.04</v>
       </c>
       <c r="I312" s="45">
-        <v>1.3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="J312" s="45"/>
-      <c r="K312" s="46">
-        <v>45222</v>
-      </c>
-      <c r="L312" s="44" t="s">
-        <v>349</v>
-      </c>
-      <c r="M312" s="44"/>
+      <c r="K312" s="46"/>
+      <c r="L312" s="44"/>
+      <c r="M312" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" s="44" t="s">
         <v>350</v>
       </c>
-      <c r="B313" s="45">
-        <v>371</v>
-      </c>
-      <c r="C313" s="45">
-        <v>1.5</v>
-      </c>
-      <c r="D313" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="E313" s="45">
-        <v>74.67</v>
-      </c>
-      <c r="F313" s="45">
-        <v>2.67</v>
-      </c>
-      <c r="G313" s="45">
-        <v>3.2</v>
-      </c>
-      <c r="H313" s="45">
-        <v>13.04</v>
-      </c>
-      <c r="I313" s="45">
-        <v>6.0000000000000001E-3</v>
-      </c>
+      <c r="B313" s="45"/>
+      <c r="C313" s="45"/>
+      <c r="D313" s="45"/>
+      <c r="E313" s="45"/>
+      <c r="F313" s="45"/>
+      <c r="G313" s="45"/>
+      <c r="H313" s="45"/>
+      <c r="I313" s="45"/>
       <c r="J313" s="45"/>
       <c r="K313" s="46"/>
       <c r="L313" s="44"/>
-      <c r="M313" s="44"/>
+      <c r="M313" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="B314" s="45"/>
-      <c r="C314" s="45"/>
-      <c r="D314" s="45"/>
-      <c r="E314" s="45"/>
-      <c r="F314" s="45"/>
-      <c r="G314" s="45"/>
-      <c r="H314" s="45"/>
-      <c r="I314" s="45"/>
+      <c r="B314" s="45">
+        <v>548</v>
+      </c>
+      <c r="C314" s="45">
+        <v>29</v>
+      </c>
+      <c r="D314" s="45">
+        <v>15</v>
+      </c>
+      <c r="E314" s="45">
+        <v>56</v>
+      </c>
+      <c r="F314" s="45">
+        <v>4.2</v>
+      </c>
+      <c r="G314" s="45">
+        <v>0</v>
+      </c>
+      <c r="H314" s="45">
+        <v>16</v>
+      </c>
+      <c r="I314" s="45">
+        <v>0.01</v>
+      </c>
       <c r="J314" s="45"/>
-      <c r="K314" s="46"/>
+      <c r="K314" s="46">
+        <v>45538</v>
+      </c>
       <c r="L314" s="44"/>
-      <c r="M314" s="44"/>
+      <c r="M314" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" s="44" t="s">
         <v>352</v>
       </c>
       <c r="B315" s="45">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C315" s="45">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D315" s="45">
-        <v>15</v>
+        <v>0.7</v>
       </c>
       <c r="E315" s="45">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F315" s="45">
-        <v>4.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G315" s="45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H315" s="45">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="I315" s="45">
-        <v>0.01</v>
+        <v>1.7</v>
       </c>
       <c r="J315" s="45"/>
       <c r="K315" s="46">
-        <v>45538</v>
+        <v>45184</v>
       </c>
       <c r="L315" s="44"/>
-      <c r="M315" s="44"/>
+      <c r="M315" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" s="44" t="s">
         <v>353</v>
       </c>
       <c r="B316" s="45">
-        <v>545</v>
+        <v>660</v>
       </c>
       <c r="C316" s="45">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D316" s="45">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="E316" s="45">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F316" s="45">
-        <v>1.1000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="G316" s="45">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="H316" s="45">
-        <v>3.5</v>
+        <v>22.57</v>
       </c>
       <c r="I316" s="45">
         <v>1.7</v>
       </c>
       <c r="J316" s="45"/>
       <c r="K316" s="46">
-        <v>45184</v>
+        <v>45180</v>
       </c>
       <c r="L316" s="44"/>
-      <c r="M316" s="44"/>
+      <c r="M316" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" s="44" t="s">
         <v>354</v>
       </c>
-      <c r="B317" s="45">
-        <v>660</v>
-      </c>
-      <c r="C317" s="45">
-        <v>30</v>
-      </c>
-      <c r="D317" s="45">
-        <v>14</v>
-      </c>
-      <c r="E317" s="45">
-        <v>73</v>
-      </c>
-      <c r="F317" s="45">
-        <v>2.5</v>
-      </c>
-      <c r="G317" s="45">
-        <v>3.6</v>
-      </c>
-      <c r="H317" s="45">
-        <v>22.57</v>
-      </c>
-      <c r="I317" s="45">
-        <v>1.7</v>
-      </c>
+      <c r="B317" s="45"/>
+      <c r="C317" s="45"/>
+      <c r="D317" s="45"/>
+      <c r="E317" s="45"/>
+      <c r="F317" s="45"/>
+      <c r="G317" s="45"/>
+      <c r="H317" s="45"/>
+      <c r="I317" s="45"/>
       <c r="J317" s="45"/>
-      <c r="K317" s="46">
-        <v>45180</v>
-      </c>
+      <c r="K317" s="46"/>
       <c r="L317" s="44"/>
-      <c r="M317" s="44"/>
+      <c r="M317" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="B318" s="45"/>
-      <c r="C318" s="45"/>
-      <c r="D318" s="45"/>
-      <c r="E318" s="45"/>
-      <c r="F318" s="45"/>
-      <c r="G318" s="45"/>
-      <c r="H318" s="45"/>
-      <c r="I318" s="45"/>
+      <c r="B318" s="45">
+        <v>100</v>
+      </c>
+      <c r="C318" s="45">
+        <v>0.1</v>
+      </c>
+      <c r="D318" s="45">
+        <v>0</v>
+      </c>
+      <c r="E318" s="45">
+        <v>21</v>
+      </c>
+      <c r="F318" s="45">
+        <v>1.7</v>
+      </c>
+      <c r="G318" s="45">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H318" s="45">
+        <v>2.48</v>
+      </c>
+      <c r="I318" s="45">
+        <v>0.69</v>
+      </c>
       <c r="J318" s="45"/>
-      <c r="K318" s="46"/>
+      <c r="K318" s="46">
+        <v>45225</v>
+      </c>
       <c r="L318" s="44"/>
-      <c r="M318" s="44"/>
+      <c r="M318" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" s="44" t="s">
         <v>356</v>
       </c>
       <c r="B319" s="45">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C319" s="45">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="D319" s="45">
         <v>0</v>
       </c>
       <c r="E319" s="45">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F319" s="45">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G319" s="45">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H319" s="45">
-        <v>2.48</v>
+        <v>30.2</v>
       </c>
       <c r="I319" s="45">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="J319" s="45"/>
-      <c r="K319" s="46">
-        <v>45225</v>
-      </c>
+      <c r="K319" s="46"/>
       <c r="L319" s="44"/>
-      <c r="M319" s="44"/>
+      <c r="M319" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" s="44" t="s">
         <v>357</v>
       </c>
       <c r="B320" s="45">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C320" s="45">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D320" s="45">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E320" s="45">
         <v>0</v>
@@ -12917,1122 +13023,1232 @@
         <v>0</v>
       </c>
       <c r="H320" s="45">
-        <v>30.2</v>
+        <v>24</v>
       </c>
       <c r="I320" s="45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J320" s="45"/>
-      <c r="K320" s="46"/>
+      <c r="K320" s="46">
+        <v>45222</v>
+      </c>
       <c r="L320" s="44"/>
-      <c r="M320" s="44"/>
+      <c r="M320" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" s="44" t="s">
         <v>358</v>
       </c>
       <c r="B321" s="45">
-        <v>107</v>
+        <v>348</v>
       </c>
       <c r="C321" s="45">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="D321" s="45">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="E321" s="45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F321" s="45">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G321" s="45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H321" s="45">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="I321" s="45">
-        <v>1.2</v>
+        <v>4.75</v>
       </c>
       <c r="J321" s="45"/>
-      <c r="K321" s="46">
-        <v>45222</v>
-      </c>
+      <c r="K321" s="46"/>
       <c r="L321" s="44"/>
-      <c r="M321" s="44"/>
+      <c r="M321" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" s="44" t="s">
         <v>359</v>
       </c>
       <c r="B322" s="45">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="C322" s="45">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="D322" s="45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E322" s="45">
-        <v>50</v>
+        <v>35.5</v>
       </c>
       <c r="F322" s="45">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G322" s="45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H322" s="45">
-        <v>6.8</v>
+        <v>13.3</v>
       </c>
       <c r="I322" s="45">
-        <v>4.75</v>
+        <v>0.1</v>
       </c>
       <c r="J322" s="45"/>
-      <c r="K322" s="46"/>
-      <c r="L322" s="44"/>
-      <c r="M322" s="44"/>
+      <c r="K322" s="46">
+        <v>45206</v>
+      </c>
+      <c r="L322" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="M322" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" s="44" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B323" s="45">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="C323" s="45">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="D323" s="45">
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E323" s="45">
-        <v>35.5</v>
+        <v>23</v>
       </c>
       <c r="F323" s="45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="G323" s="45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H323" s="45">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="I323" s="45">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J323" s="45"/>
       <c r="K323" s="46">
-        <v>45206</v>
-      </c>
-      <c r="L323" s="44" t="s">
-        <v>361</v>
-      </c>
-      <c r="M323" s="44"/>
+        <v>45223</v>
+      </c>
+      <c r="L323" s="44"/>
+      <c r="M323" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" s="44" t="s">
         <v>362</v>
       </c>
       <c r="B324" s="45">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="C324" s="45">
-        <v>11</v>
+        <v>0.31</v>
       </c>
       <c r="D324" s="45">
-        <v>4.9000000000000004</v>
+        <v>0.04</v>
       </c>
       <c r="E324" s="45">
-        <v>23</v>
+        <v>17.73</v>
       </c>
       <c r="F324" s="45">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="G324" s="45">
-        <v>1.7</v>
+        <v>0.49</v>
       </c>
       <c r="H324" s="45">
-        <v>12</v>
+        <v>1.97</v>
       </c>
       <c r="I324" s="45">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="J324" s="45"/>
       <c r="K324" s="46">
-        <v>45223</v>
-      </c>
-      <c r="L324" s="44"/>
-      <c r="M324" s="44"/>
+        <v>45183</v>
+      </c>
+      <c r="L324" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="M324" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" s="44" t="s">
-        <v>363</v>
+        <v>151</v>
       </c>
       <c r="B325" s="45">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="C325" s="45">
-        <v>0.31</v>
-      </c>
-      <c r="D325" s="45">
-        <v>0.04</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D325" s="45"/>
       <c r="E325" s="45">
-        <v>17.73</v>
+        <v>0.9</v>
       </c>
       <c r="F325" s="45">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="G325" s="45">
-        <v>0.49</v>
+        <v>2.6</v>
       </c>
       <c r="H325" s="45">
-        <v>1.97</v>
+        <v>19.8</v>
       </c>
       <c r="I325" s="45">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J325" s="45"/>
-      <c r="K325" s="46">
-        <v>45183</v>
-      </c>
-      <c r="L325" s="44" t="s">
-        <v>364</v>
-      </c>
-      <c r="M325" s="44"/>
+      <c r="K325" s="46"/>
+      <c r="L325" s="44"/>
+      <c r="M325" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B326" s="45">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="C326" s="45">
-        <v>12</v>
-      </c>
-      <c r="D326" s="45"/>
+        <v>13.7</v>
+      </c>
+      <c r="D326" s="45">
+        <v>4.8</v>
+      </c>
       <c r="E326" s="45">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F326" s="45">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G326" s="45">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H326" s="45">
-        <v>19.8</v>
+        <v>27.8</v>
       </c>
       <c r="I326" s="45">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J326" s="45"/>
-      <c r="K326" s="46"/>
+      <c r="K326" s="46">
+        <v>45181</v>
+      </c>
       <c r="L326" s="44"/>
-      <c r="M326" s="44"/>
+      <c r="M326" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" s="44" t="s">
-        <v>149</v>
+        <v>364</v>
       </c>
       <c r="B327" s="45">
-        <v>235</v>
+        <v>69</v>
       </c>
       <c r="C327" s="45">
-        <v>13.7</v>
+        <v>1</v>
       </c>
       <c r="D327" s="45">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="E327" s="45">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="F327" s="45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G327" s="45">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H327" s="45">
-        <v>27.8</v>
+        <v>3</v>
       </c>
       <c r="I327" s="45">
-        <v>2.4</v>
+        <v>0.06</v>
       </c>
       <c r="J327" s="45"/>
-      <c r="K327" s="46">
-        <v>45181</v>
-      </c>
+      <c r="K327" s="46"/>
       <c r="L327" s="44"/>
-      <c r="M327" s="44"/>
+      <c r="M327" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" s="44" t="s">
         <v>365</v>
       </c>
-      <c r="B328" s="45"/>
-      <c r="C328" s="45"/>
-      <c r="D328" s="45"/>
-      <c r="E328" s="45"/>
-      <c r="F328" s="45"/>
-      <c r="G328" s="45"/>
-      <c r="H328" s="45"/>
-      <c r="I328" s="45"/>
+      <c r="B328" s="45">
+        <v>196</v>
+      </c>
+      <c r="C328" s="45">
+        <v>15.4</v>
+      </c>
+      <c r="D328" s="45">
+        <v>0</v>
+      </c>
+      <c r="E328" s="45">
+        <v>1.9</v>
+      </c>
+      <c r="F328" s="45">
+        <v>1.9</v>
+      </c>
+      <c r="G328" s="45">
+        <v>0.9</v>
+      </c>
+      <c r="H328" s="45">
+        <v>12</v>
+      </c>
+      <c r="I328" s="45">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J328" s="45"/>
-      <c r="K328" s="46"/>
+      <c r="K328" s="46">
+        <v>45190</v>
+      </c>
       <c r="L328" s="44"/>
-      <c r="M328" s="44"/>
+      <c r="M328" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" s="44" t="s">
         <v>366</v>
       </c>
       <c r="B329" s="45">
-        <v>69</v>
+        <v>493</v>
       </c>
       <c r="C329" s="45">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D329" s="45">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="E329" s="45">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="F329" s="45">
+        <v>28</v>
+      </c>
+      <c r="G329" s="45">
         <v>3.5</v>
       </c>
-      <c r="G329" s="45">
-        <v>7.7</v>
-      </c>
       <c r="H329" s="45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I329" s="45">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="J329" s="45"/>
-      <c r="K329" s="46"/>
-      <c r="L329" s="44"/>
-      <c r="M329" s="44"/>
+      <c r="K329" s="46">
+        <v>45700</v>
+      </c>
+      <c r="L329" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="M329" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330" s="44" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B330" s="45">
-        <v>196</v>
+        <v>350</v>
       </c>
       <c r="C330" s="45">
-        <v>15.4</v>
+        <v>0.6</v>
       </c>
       <c r="D330" s="45">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E330" s="45">
-        <v>1.9</v>
+        <v>78</v>
       </c>
       <c r="F330" s="45">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="G330" s="45">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H330" s="45">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="I330" s="45">
-        <v>1.1000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="J330" s="45"/>
       <c r="K330" s="46">
-        <v>45190</v>
+        <v>45216</v>
       </c>
       <c r="L330" s="44"/>
-      <c r="M330" s="44"/>
+      <c r="M330" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" s="44" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B331" s="45">
-        <v>493</v>
+        <v>137</v>
       </c>
       <c r="C331" s="45">
-        <v>22</v>
-      </c>
-      <c r="D331" s="45">
-        <v>4</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="D331" s="45"/>
       <c r="E331" s="45">
-        <v>66</v>
+        <v>25.2</v>
       </c>
       <c r="F331" s="45">
-        <v>28</v>
+        <v>0.2</v>
       </c>
       <c r="G331" s="45">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="H331" s="45">
-        <v>6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I331" s="45">
-        <v>0.45</v>
+        <v>3.3E-3</v>
       </c>
       <c r="J331" s="45"/>
       <c r="K331" s="46">
-        <v>45700</v>
-      </c>
-      <c r="L331" s="44" t="s">
-        <v>369</v>
-      </c>
-      <c r="M331" s="44"/>
+        <v>45183</v>
+      </c>
+      <c r="L331" s="44"/>
+      <c r="M331" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" s="44" t="s">
         <v>370</v>
       </c>
       <c r="B332" s="45">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="C332" s="45">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="D332" s="45">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E332" s="45">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F332" s="45">
-        <v>0.3</v>
+        <v>20</v>
       </c>
       <c r="G332" s="45">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H332" s="45">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I332" s="45">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="J332" s="45"/>
       <c r="K332" s="46">
-        <v>45216</v>
+        <v>45539</v>
       </c>
       <c r="L332" s="44"/>
-      <c r="M332" s="44"/>
+      <c r="M332" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" s="44" t="s">
         <v>371</v>
       </c>
       <c r="B333" s="45">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C333" s="45">
-        <v>2.8</v>
-      </c>
-      <c r="D333" s="45"/>
+        <v>6.3</v>
+      </c>
+      <c r="D333" s="45">
+        <v>2.37</v>
+      </c>
       <c r="E333" s="45">
-        <v>25.2</v>
+        <v>0</v>
       </c>
       <c r="F333" s="45">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G333" s="45">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H333" s="45">
-        <v>2.2000000000000002</v>
+        <v>19.25</v>
       </c>
       <c r="I333" s="45">
-        <v>3.3E-3</v>
+        <v>0.19</v>
       </c>
       <c r="J333" s="45"/>
       <c r="K333" s="46">
-        <v>45183</v>
+        <v>45189</v>
       </c>
       <c r="L333" s="44"/>
-      <c r="M333" s="44"/>
+      <c r="M333" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" s="44" t="s">
         <v>372</v>
       </c>
       <c r="B334" s="45">
-        <v>381</v>
+        <v>117</v>
       </c>
       <c r="C334" s="45">
-        <v>3</v>
+        <v>4.32</v>
       </c>
       <c r="D334" s="45">
         <v>1</v>
       </c>
       <c r="E334" s="45">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F334" s="45">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G334" s="45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H334" s="45">
-        <v>7</v>
-      </c>
-      <c r="I334" s="45">
-        <v>0.5</v>
-      </c>
+        <v>18.28</v>
+      </c>
+      <c r="I334" s="45"/>
       <c r="J334" s="45"/>
       <c r="K334" s="46">
-        <v>45539</v>
+        <v>45187</v>
       </c>
       <c r="L334" s="44"/>
-      <c r="M334" s="44"/>
+      <c r="M334" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" s="44" t="s">
         <v>373</v>
       </c>
       <c r="B335" s="45">
-        <v>139</v>
+        <v>369</v>
       </c>
       <c r="C335" s="45">
-        <v>6.3</v>
+        <v>23.5</v>
       </c>
       <c r="D335" s="45">
-        <v>2.37</v>
+        <v>4.8</v>
       </c>
       <c r="E335" s="45">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="F335" s="45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="G335" s="45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H335" s="45">
-        <v>19.25</v>
+        <v>4.3</v>
       </c>
       <c r="I335" s="45">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="J335" s="45"/>
       <c r="K335" s="46">
-        <v>45189</v>
+        <v>45539</v>
       </c>
       <c r="L335" s="44"/>
-      <c r="M335" s="44"/>
+      <c r="M335" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="B336" s="45"/>
-      <c r="C336" s="45"/>
-      <c r="D336" s="45"/>
-      <c r="E336" s="45"/>
-      <c r="F336" s="45"/>
-      <c r="G336" s="45"/>
-      <c r="H336" s="45"/>
-      <c r="I336" s="45"/>
+        <v>374</v>
+      </c>
+      <c r="B336" s="45">
+        <v>163</v>
+      </c>
+      <c r="C336" s="45">
+        <v>9.6</v>
+      </c>
+      <c r="D336" s="45">
+        <v>2</v>
+      </c>
+      <c r="E336" s="45">
+        <v>7.9</v>
+      </c>
+      <c r="F336" s="45">
+        <v>1.3</v>
+      </c>
+      <c r="G336" s="45">
+        <v>0</v>
+      </c>
+      <c r="H336" s="45">
+        <v>9.9</v>
+      </c>
+      <c r="I336" s="45">
+        <v>0.1</v>
+      </c>
       <c r="J336" s="45"/>
-      <c r="K336" s="46"/>
+      <c r="K336" s="46">
+        <v>45215</v>
+      </c>
       <c r="L336" s="44"/>
-      <c r="M336" s="44"/>
+      <c r="M336" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" s="44" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B337" s="45">
-        <v>117</v>
+        <v>348</v>
       </c>
       <c r="C337" s="45">
-        <v>4.32</v>
+        <v>20</v>
       </c>
       <c r="D337" s="45">
-        <v>1</v>
+        <v>4.1059999999999999</v>
       </c>
       <c r="E337" s="45">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F337" s="45">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G337" s="45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H337" s="45">
-        <v>18.28</v>
-      </c>
-      <c r="I337" s="45"/>
+        <v>7.6</v>
+      </c>
+      <c r="I337" s="45">
+        <v>0.86</v>
+      </c>
       <c r="J337" s="45"/>
       <c r="K337" s="46">
-        <v>45187</v>
+        <v>45219</v>
       </c>
       <c r="L337" s="44"/>
-      <c r="M337" s="44"/>
+      <c r="M337" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" s="44" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B338" s="45">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="C338" s="45">
-        <v>26</v>
+        <v>18.7</v>
       </c>
       <c r="D338" s="45">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E338" s="45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F338" s="45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G338" s="45">
         <v>0</v>
       </c>
       <c r="H338" s="45">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I338" s="45"/>
       <c r="J338" s="45"/>
-      <c r="K338" s="46"/>
-      <c r="L338" s="44"/>
-      <c r="M338" s="44"/>
+      <c r="K338" s="46">
+        <v>45510</v>
+      </c>
+      <c r="L338" s="44" t="s">
+        <v>377</v>
+      </c>
+      <c r="M338" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" s="44" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B339" s="45">
-        <v>369</v>
+        <f>357</f>
+        <v>357</v>
       </c>
       <c r="C339" s="45">
-        <v>23.5</v>
+        <f>1.5</f>
+        <v>1.5</v>
       </c>
       <c r="D339" s="45">
-        <v>4.8</v>
+        <f>0.3</f>
+        <v>0.3</v>
       </c>
       <c r="E339" s="45">
-        <v>31.3</v>
+        <f>69</f>
+        <v>69</v>
       </c>
       <c r="F339" s="45">
-        <v>2.4</v>
+        <f>1.4</f>
+        <v>1.4</v>
       </c>
       <c r="G339" s="45">
-        <v>3.4</v>
+        <f>3.5</f>
+        <v>3.5</v>
       </c>
       <c r="H339" s="45">
-        <v>4.3</v>
+        <f>15</f>
+        <v>15</v>
       </c>
       <c r="I339" s="45">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="J339" s="45"/>
       <c r="K339" s="46">
-        <v>45539</v>
+        <v>45189</v>
       </c>
       <c r="L339" s="44"/>
-      <c r="M339" s="44"/>
+      <c r="M339" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" s="44" t="s">
-        <v>377</v>
+        <v>155</v>
       </c>
       <c r="B340" s="45">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="C340" s="45">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="D340" s="45">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="E340" s="45">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="F340" s="45">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="G340" s="45">
         <v>0</v>
       </c>
       <c r="H340" s="45">
-        <v>9.9</v>
+        <v>31</v>
       </c>
       <c r="I340" s="45">
-        <v>0.1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J340" s="45"/>
       <c r="K340" s="46">
-        <v>45215</v>
+        <v>45188</v>
       </c>
       <c r="L340" s="44"/>
-      <c r="M340" s="44"/>
+      <c r="M340" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" s="44" t="s">
-        <v>378</v>
+        <v>193</v>
       </c>
       <c r="B341" s="45">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="C341" s="45">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D341" s="45">
-        <v>4.1059999999999999</v>
+        <v>19</v>
       </c>
       <c r="E341" s="45">
-        <v>34</v>
+        <v>2.6</v>
       </c>
       <c r="F341" s="45">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="G341" s="45">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H341" s="45">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="I341" s="45">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="J341" s="45"/>
       <c r="K341" s="46">
-        <v>45219</v>
+        <v>45537</v>
       </c>
       <c r="L341" s="44"/>
-      <c r="M341" s="44"/>
+      <c r="M341" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" s="44" t="s">
         <v>379</v>
       </c>
       <c r="B342" s="45">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C342" s="45">
-        <v>18.7</v>
+        <v>20</v>
       </c>
       <c r="D342" s="45">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="E342" s="45">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="F342" s="45">
-        <v>3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G342" s="45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H342" s="45">
-        <v>17</v>
-      </c>
-      <c r="I342" s="45"/>
+        <v>2.4</v>
+      </c>
+      <c r="I342" s="45">
+        <v>1.2</v>
+      </c>
       <c r="J342" s="45"/>
       <c r="K342" s="46">
-        <v>45510</v>
-      </c>
-      <c r="L342" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M342" s="44"/>
+        <v>45194</v>
+      </c>
+      <c r="L342" s="44"/>
+      <c r="M342" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" s="44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B343" s="45">
-        <f>357</f>
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="C343" s="45">
-        <f>1.5</f>
+        <v>3.5</v>
+      </c>
+      <c r="D343" s="45">
+        <v>0.6</v>
+      </c>
+      <c r="E343" s="45">
+        <v>7.5</v>
+      </c>
+      <c r="F343" s="45">
+        <v>6</v>
+      </c>
+      <c r="G343" s="45">
+        <v>2</v>
+      </c>
+      <c r="H343" s="45">
         <v>1.5</v>
       </c>
-      <c r="D343" s="45">
-        <f>0.3</f>
-        <v>0.3</v>
-      </c>
-      <c r="E343" s="45">
-        <f>69</f>
-        <v>69</v>
-      </c>
-      <c r="F343" s="45">
-        <f>1.4</f>
-        <v>1.4</v>
-      </c>
-      <c r="G343" s="45">
-        <f>3.5</f>
-        <v>3.5</v>
-      </c>
-      <c r="H343" s="45">
-        <f>15</f>
-        <v>15</v>
-      </c>
       <c r="I343" s="45">
-        <v>0.46</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J343" s="45"/>
       <c r="K343" s="46">
-        <v>45189</v>
-      </c>
-      <c r="L343" s="44"/>
-      <c r="M343" s="44"/>
+        <v>45182</v>
+      </c>
+      <c r="L343" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="M343" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" s="44" t="s">
-        <v>155</v>
+        <v>382</v>
       </c>
       <c r="B344" s="45">
-        <v>297</v>
+        <v>470</v>
       </c>
       <c r="C344" s="45">
-        <v>19</v>
+        <v>15.7</v>
       </c>
       <c r="D344" s="45">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="E344" s="45">
-        <v>0.5</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="F344" s="45">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="G344" s="45">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H344" s="45">
-        <v>31</v>
+        <v>7.5</v>
       </c>
       <c r="I344" s="45">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J344" s="45"/>
+        <v>2.5</v>
+      </c>
+      <c r="J344" s="45">
+        <v>0.54</v>
+      </c>
       <c r="K344" s="46">
-        <v>45188</v>
-      </c>
-      <c r="L344" s="44"/>
-      <c r="M344" s="44"/>
+        <v>45179</v>
+      </c>
+      <c r="L344" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="M344" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" s="44" t="s">
-        <v>193</v>
+        <v>384</v>
       </c>
       <c r="B345" s="45">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="C345" s="45">
-        <v>27</v>
+        <v>18.2</v>
       </c>
       <c r="D345" s="45">
-        <v>19</v>
+        <v>10.53</v>
       </c>
       <c r="E345" s="45">
-        <v>2.6</v>
+        <v>24.41</v>
       </c>
       <c r="F345" s="45">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="G345" s="45">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H345" s="45">
-        <v>14</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="I345" s="45">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
       <c r="J345" s="45"/>
       <c r="K345" s="46">
-        <v>45537</v>
+        <v>45218</v>
       </c>
       <c r="L345" s="44"/>
-      <c r="M345" s="44"/>
+      <c r="M345" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A346" s="44" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B346" s="45">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="C346" s="45">
-        <v>20</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D346" s="45">
-        <v>6.9</v>
+        <v>3.6</v>
       </c>
       <c r="E346" s="45">
-        <v>3.7</v>
+        <v>39</v>
       </c>
       <c r="F346" s="45">
-        <v>2.2999999999999998</v>
+        <v>3.4</v>
       </c>
       <c r="G346" s="45">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H346" s="45">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="I346" s="45">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J346" s="45"/>
       <c r="K346" s="46">
-        <v>45194</v>
-      </c>
-      <c r="L346" s="44"/>
-      <c r="M346" s="44"/>
+        <v>45210</v>
+      </c>
+      <c r="L346" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="M346" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A347" s="44" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B347" s="45">
-        <v>74</v>
+        <v>461</v>
       </c>
       <c r="C347" s="45">
+        <v>18</v>
+      </c>
+      <c r="D347" s="45">
+        <v>1.7</v>
+      </c>
+      <c r="E347" s="45">
+        <v>65</v>
+      </c>
+      <c r="F347" s="45">
+        <v>9.1</v>
+      </c>
+      <c r="G347" s="45">
         <v>3.5</v>
       </c>
-      <c r="D347" s="45">
-        <v>0.6</v>
-      </c>
-      <c r="E347" s="45">
-        <v>7.5</v>
-      </c>
-      <c r="F347" s="45">
-        <v>6</v>
-      </c>
-      <c r="G347" s="45">
-        <v>2</v>
-      </c>
       <c r="H347" s="45">
-        <v>1.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I347" s="45">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J347" s="45"/>
+        <v>1.71</v>
+      </c>
+      <c r="J347" s="45">
+        <v>0.77</v>
+      </c>
       <c r="K347" s="46">
-        <v>45182</v>
+        <v>45179</v>
       </c>
       <c r="L347" s="44" t="s">
-        <v>384</v>
-      </c>
-      <c r="M347" s="44"/>
+        <v>388</v>
+      </c>
+      <c r="M347" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A348" s="44" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B348" s="45">
-        <v>470</v>
+        <v>427</v>
       </c>
       <c r="C348" s="45">
-        <v>15.7</v>
+        <v>5</v>
       </c>
       <c r="D348" s="45">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="E348" s="45">
-        <v>74.400000000000006</v>
-      </c>
-      <c r="F348" s="45">
-        <v>1.9</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="F348" s="45"/>
       <c r="G348" s="45">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H348" s="45">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="I348" s="45">
         <v>2.5</v>
       </c>
-      <c r="J348" s="45">
-        <v>0.54</v>
-      </c>
+      <c r="J348" s="45"/>
       <c r="K348" s="46">
-        <v>45179</v>
-      </c>
-      <c r="L348" s="44" t="s">
-        <v>386</v>
-      </c>
-      <c r="M348" s="44"/>
+        <v>45184</v>
+      </c>
+      <c r="L348" s="44"/>
+      <c r="M348" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" s="44" t="s">
-        <v>387</v>
+        <v>209</v>
       </c>
       <c r="B349" s="45">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="C349" s="45">
-        <v>18.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D349" s="45">
-        <v>10.53</v>
+        <v>3.17</v>
       </c>
       <c r="E349" s="45">
-        <v>24.41</v>
+        <v>0</v>
       </c>
       <c r="F349" s="45">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G349" s="45">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H349" s="45">
-        <v>4.7699999999999996</v>
+        <v>12.4</v>
       </c>
       <c r="I349" s="45">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="J349" s="45"/>
-      <c r="K349" s="46">
-        <v>45218</v>
-      </c>
-      <c r="L349" s="44"/>
-      <c r="M349" s="44"/>
+      <c r="K349" s="46"/>
+      <c r="L349" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="M349" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" s="44" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B350" s="45">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="C350" s="45">
-        <v>9.8000000000000007</v>
+        <v>7.5</v>
       </c>
       <c r="D350" s="45">
-        <v>3.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E350" s="45">
-        <v>39</v>
+        <v>0.6</v>
       </c>
       <c r="F350" s="45">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G350" s="45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H350" s="45">
-        <v>13</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I350" s="45">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J350" s="45"/>
       <c r="K350" s="46">
-        <v>45210</v>
-      </c>
-      <c r="L350" s="44" t="s">
-        <v>389</v>
-      </c>
-      <c r="M350" s="44"/>
+        <v>45189</v>
+      </c>
+      <c r="L350" s="44"/>
+      <c r="M350" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="44" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B351" s="45">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C351" s="45">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D351" s="45">
-        <v>1.7</v>
+        <v>21</v>
       </c>
       <c r="E351" s="45">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F351" s="45">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G351" s="45">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H351" s="45">
-        <v>8.3000000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I351" s="45">
-        <v>1.71</v>
-      </c>
-      <c r="J351" s="45">
-        <v>0.77</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="J351" s="45"/>
       <c r="K351" s="46">
-        <v>45179</v>
-      </c>
-      <c r="L351" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="M351" s="44"/>
+        <v>45202</v>
+      </c>
+      <c r="L351" s="44"/>
+      <c r="M351" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" s="44" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B352" s="45">
-        <v>427</v>
+        <v>517</v>
       </c>
       <c r="C352" s="45">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D352" s="45">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E352" s="45">
-        <v>21.5</v>
-      </c>
-      <c r="F352" s="45"/>
+        <v>58</v>
+      </c>
+      <c r="F352" s="45">
+        <v>25</v>
+      </c>
       <c r="G352" s="45">
         <v>0</v>
       </c>
       <c r="H352" s="45">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="I352" s="45">
-        <v>2.5</v>
+        <v>0.37</v>
       </c>
       <c r="J352" s="45"/>
       <c r="K352" s="46">
-        <v>45184</v>
-      </c>
-      <c r="L352" s="44"/>
-      <c r="M352" s="44"/>
+        <v>45211</v>
+      </c>
+      <c r="L352" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="M352" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="44" t="s">
-        <v>209</v>
+        <v>395</v>
       </c>
       <c r="B353" s="45">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="C353" s="45">
-        <v>8.6999999999999993</v>
+        <v>22.2</v>
       </c>
       <c r="D353" s="45">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="E353" s="45">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F353" s="45">
         <v>0</v>
@@ -14041,176 +14257,36 @@
         <v>0</v>
       </c>
       <c r="H353" s="45">
-        <v>12.4</v>
+        <v>14.6</v>
       </c>
       <c r="I353" s="45">
         <v>0</v>
       </c>
       <c r="J353" s="45"/>
-      <c r="K353" s="46"/>
+      <c r="K353" s="46">
+        <v>45201</v>
+      </c>
       <c r="L353" s="44" t="s">
-        <v>393</v>
-      </c>
-      <c r="M353" s="44"/>
+        <v>396</v>
+      </c>
+      <c r="M353" s="44" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A354" s="44" t="s">
-        <v>394</v>
-      </c>
-      <c r="B354" s="45">
-        <v>107</v>
-      </c>
-      <c r="C354" s="45">
-        <v>7.5</v>
-      </c>
-      <c r="D354" s="45">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E354" s="45">
-        <v>0.6</v>
-      </c>
-      <c r="F354" s="45">
-        <v>0</v>
-      </c>
-      <c r="G354" s="45">
-        <v>0</v>
-      </c>
-      <c r="H354" s="45">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="I354" s="45">
-        <v>1.4</v>
-      </c>
+      <c r="A354" s="44"/>
+      <c r="B354" s="45"/>
+      <c r="C354" s="45"/>
+      <c r="D354" s="45"/>
+      <c r="E354" s="45"/>
+      <c r="F354" s="45"/>
+      <c r="G354" s="45"/>
+      <c r="H354" s="45"/>
+      <c r="I354" s="45"/>
       <c r="J354" s="45"/>
-      <c r="K354" s="46">
-        <v>45189</v>
-      </c>
+      <c r="K354" s="46"/>
       <c r="L354" s="44"/>
       <c r="M354" s="44"/>
-    </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A355" s="44" t="s">
-        <v>395</v>
-      </c>
-      <c r="B355" s="45">
-        <v>501</v>
-      </c>
-      <c r="C355" s="45">
-        <v>25</v>
-      </c>
-      <c r="D355" s="45">
-        <v>21</v>
-      </c>
-      <c r="E355" s="45">
-        <v>58</v>
-      </c>
-      <c r="F355" s="45">
-        <v>25</v>
-      </c>
-      <c r="G355" s="45">
-        <v>0</v>
-      </c>
-      <c r="H355" s="45">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I355" s="45">
-        <v>0.35</v>
-      </c>
-      <c r="J355" s="45"/>
-      <c r="K355" s="46">
-        <v>45202</v>
-      </c>
-      <c r="L355" s="44"/>
-      <c r="M355" s="44"/>
-    </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A356" s="44" t="s">
-        <v>396</v>
-      </c>
-      <c r="B356" s="45">
-        <v>517</v>
-      </c>
-      <c r="C356" s="45">
-        <v>27</v>
-      </c>
-      <c r="D356" s="45">
-        <v>19</v>
-      </c>
-      <c r="E356" s="45">
-        <v>58</v>
-      </c>
-      <c r="F356" s="45">
-        <v>25</v>
-      </c>
-      <c r="G356" s="45">
-        <v>0</v>
-      </c>
-      <c r="H356" s="45">
-        <v>8.6</v>
-      </c>
-      <c r="I356" s="45">
-        <v>0.37</v>
-      </c>
-      <c r="J356" s="45"/>
-      <c r="K356" s="46">
-        <v>45211</v>
-      </c>
-      <c r="L356" s="44" t="s">
-        <v>397</v>
-      </c>
-      <c r="M356" s="44"/>
-    </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A357" s="44" t="s">
-        <v>398</v>
-      </c>
-      <c r="B357" s="45">
-        <v>259</v>
-      </c>
-      <c r="C357" s="45">
-        <v>22.2</v>
-      </c>
-      <c r="D357" s="45">
-        <v>0</v>
-      </c>
-      <c r="E357" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="F357" s="45">
-        <v>0</v>
-      </c>
-      <c r="G357" s="45">
-        <v>0</v>
-      </c>
-      <c r="H357" s="45">
-        <v>14.6</v>
-      </c>
-      <c r="I357" s="45">
-        <v>0</v>
-      </c>
-      <c r="J357" s="45"/>
-      <c r="K357" s="46">
-        <v>45201</v>
-      </c>
-      <c r="L357" s="44" t="s">
-        <v>399</v>
-      </c>
-      <c r="M357" s="44"/>
-    </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A358" s="44"/>
-      <c r="B358" s="45"/>
-      <c r="C358" s="45"/>
-      <c r="D358" s="45"/>
-      <c r="E358" s="45"/>
-      <c r="F358" s="45"/>
-      <c r="G358" s="45"/>
-      <c r="H358" s="45"/>
-      <c r="I358" s="45"/>
-      <c r="J358" s="45"/>
-      <c r="K358" s="46"/>
-      <c r="L358" s="44"/>
-      <c r="M358" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M270" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e36746ea3f026f8f/Documenti/GitHub/Dilah96.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8058225-7ECF-4744-8807-6A693E1C768C}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F650CB9-19B7-4B9B-8A23-F2540C30E36E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alimenti" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="401">
   <si>
     <t>Cibo</t>
   </si>
@@ -1230,6 +1230,18 @@
   </si>
   <si>
     <t>Valori per un cono(scrivere 100)</t>
+  </si>
+  <si>
+    <t>Crackers Galbusera</t>
+  </si>
+  <si>
+    <t>40 gr pacchetto</t>
+  </si>
+  <si>
+    <t>Panpiuma</t>
+  </si>
+  <si>
+    <t>35 gr una fetta</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M354"/>
+  <dimension ref="A1:M355"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -14274,19 +14286,80 @@
       </c>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A354" s="44"/>
-      <c r="B354" s="45"/>
-      <c r="C354" s="45"/>
-      <c r="D354" s="45"/>
-      <c r="E354" s="45"/>
-      <c r="F354" s="45"/>
-      <c r="G354" s="45"/>
+      <c r="A354" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="B354" s="45">
+        <v>461</v>
+      </c>
+      <c r="C354" s="45">
+        <v>18</v>
+      </c>
+      <c r="D354" s="45">
+        <v>1.8</v>
+      </c>
+      <c r="E354" s="45">
+        <v>56.9</v>
+      </c>
+      <c r="F354" s="45">
+        <v>2</v>
+      </c>
+      <c r="G354" s="45">
+        <v>6.6</v>
+      </c>
       <c r="H354" s="45"/>
-      <c r="I354" s="45"/>
+      <c r="I354" s="45">
+        <v>1.75</v>
+      </c>
       <c r="J354" s="45"/>
-      <c r="K354" s="46"/>
-      <c r="L354" s="44"/>
-      <c r="M354" s="44"/>
+      <c r="K354" s="46">
+        <v>46254</v>
+      </c>
+      <c r="L354" s="44" t="s">
+        <v>398</v>
+      </c>
+      <c r="M354" s="44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A355" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="B355" s="45">
+        <v>253</v>
+      </c>
+      <c r="C355" s="45">
+        <v>3.6</v>
+      </c>
+      <c r="D355" s="45">
+        <v>0.4</v>
+      </c>
+      <c r="E355" s="45">
+        <v>45.5</v>
+      </c>
+      <c r="F355" s="45">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G355" s="45">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H355" s="45">
+        <v>8.4</v>
+      </c>
+      <c r="I355" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="J355" s="45"/>
+      <c r="K355" s="46">
+        <v>46258</v>
+      </c>
+      <c r="L355" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="M355" s="44" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M270" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e36746ea3f026f8f/Documenti/GitHub/Dilah96.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F650CB9-19B7-4B9B-8A23-F2540C30E36E}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F8152F8-D919-4122-86B6-087AA831E937}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="402">
   <si>
     <t>Cibo</t>
   </si>
@@ -1242,6 +1242,9 @@
   </si>
   <si>
     <t>35 gr una fetta</t>
+  </si>
+  <si>
+    <t>Scamorza</t>
   </si>
 </sst>
 </file>
@@ -1751,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M355"/>
+  <dimension ref="A1:M356"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -14361,6 +14364,43 @@
         <v>14</v>
       </c>
     </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A356" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="B356" s="45">
+        <v>312</v>
+      </c>
+      <c r="C356" s="45">
+        <v>24</v>
+      </c>
+      <c r="D356" s="45">
+        <v>18</v>
+      </c>
+      <c r="E356" s="45">
+        <v>2.1</v>
+      </c>
+      <c r="F356" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="G356" s="45">
+        <v>0</v>
+      </c>
+      <c r="H356" s="45">
+        <v>22</v>
+      </c>
+      <c r="I356" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="J356" s="45"/>
+      <c r="K356" s="46">
+        <v>46258</v>
+      </c>
+      <c r="L356" s="44"/>
+      <c r="M356" s="44" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M270" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e36746ea3f026f8f/Documenti/GitHub/Dilah96.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F8152F8-D919-4122-86B6-087AA831E937}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_69FD4F923D237B0DD8AD4F917F677AD1B56B60B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9BDF29D-45C8-47E7-899A-AD96E6DA84B5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alimenti" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="408">
   <si>
     <t>Cibo</t>
   </si>
@@ -1245,6 +1245,24 @@
   </si>
   <si>
     <t>Scamorza</t>
+  </si>
+  <si>
+    <t>Sbrisolona</t>
+  </si>
+  <si>
+    <t>15g un boccone grandino</t>
+  </si>
+  <si>
+    <t>Schiacciatine classiche</t>
+  </si>
+  <si>
+    <t>37.5g pacchetto</t>
+  </si>
+  <si>
+    <t>Crackers Doria</t>
+  </si>
+  <si>
+    <t>29g pacchetto</t>
   </si>
 </sst>
 </file>
@@ -1267,12 +1285,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1754,7 +1772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M356"/>
+  <dimension ref="A1:M359"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -14401,6 +14419,123 @@
         <v>182</v>
       </c>
     </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A357" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="B357" s="45">
+        <v>487</v>
+      </c>
+      <c r="C357" s="45">
+        <v>22</v>
+      </c>
+      <c r="D357" s="45">
+        <v>9</v>
+      </c>
+      <c r="E357" s="45">
+        <v>68</v>
+      </c>
+      <c r="F357" s="45">
+        <v>23</v>
+      </c>
+      <c r="G357" s="45">
+        <v>5</v>
+      </c>
+      <c r="H357" s="45">
+        <v>7</v>
+      </c>
+      <c r="I357" s="45">
+        <v>0.34</v>
+      </c>
+      <c r="J357" s="45"/>
+      <c r="K357" s="46">
+        <v>46258</v>
+      </c>
+      <c r="L357" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="M357" s="44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A358" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="B358" s="45">
+        <v>445</v>
+      </c>
+      <c r="C358" s="45">
+        <v>15</v>
+      </c>
+      <c r="D358" s="45">
+        <v>7.6</v>
+      </c>
+      <c r="E358" s="45">
+        <v>67</v>
+      </c>
+      <c r="F358" s="45">
+        <v>2.6</v>
+      </c>
+      <c r="G358" s="45">
+        <v>2.7</v>
+      </c>
+      <c r="H358" s="45">
+        <v>10</v>
+      </c>
+      <c r="I358" s="45">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J358" s="45"/>
+      <c r="K358" s="46">
+        <v>46259</v>
+      </c>
+      <c r="L358" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="M358" s="44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A359" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="B359" s="45">
+        <v>456</v>
+      </c>
+      <c r="C359" s="45">
+        <v>15</v>
+      </c>
+      <c r="D359" s="45">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E359" s="45">
+        <v>69</v>
+      </c>
+      <c r="F359" s="45">
+        <v>1.3</v>
+      </c>
+      <c r="G359" s="45">
+        <v>2.7</v>
+      </c>
+      <c r="H359" s="45">
+        <v>9.6</v>
+      </c>
+      <c r="I359" s="45">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J359" s="45"/>
+      <c r="K359" s="46">
+        <v>46259</v>
+      </c>
+      <c r="L359" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="M359" s="44" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M270" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
